--- a/2026.02.16_Файлы загрузки и выгрузки данных/Итоги_Fuzzy RICE_один эксперт.xlsx
+++ b/2026.02.16_Файлы загрузки и выгрузки данных/Итоги_Fuzzy RICE_один эксперт.xlsx
@@ -7,7 +7,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fuzzy RICE_эксперт 1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Итоги_Fuzzy RICE_эксперт 1" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Матрица_взаимосвязей_FR" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Итоги_Fuzzy RICE_эксперт 1" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,20 +33,28 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <charset val="204"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9EAF7"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="30">
@@ -390,7 +399,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -422,46 +431,59 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -867,71 +889,71 @@
       <c r="AG2" s="41" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="31" t="n"/>
-      <c r="B3" s="42" t="inlineStr">
+      <c r="A3" s="42" t="n"/>
+      <c r="B3" s="43" t="inlineStr">
         <is>
           <t>Верхняя функция принадлежности</t>
         </is>
       </c>
-      <c r="C3" s="43" t="n"/>
-      <c r="D3" s="43" t="n"/>
-      <c r="E3" s="44" t="n"/>
-      <c r="F3" s="45" t="inlineStr">
+      <c r="C3" s="44" t="n"/>
+      <c r="D3" s="44" t="n"/>
+      <c r="E3" s="45" t="n"/>
+      <c r="F3" s="46" t="inlineStr">
         <is>
           <t>Нижняя функция принадлежности</t>
         </is>
       </c>
-      <c r="G3" s="43" t="n"/>
-      <c r="H3" s="43" t="n"/>
-      <c r="I3" s="46" t="n"/>
-      <c r="J3" s="42" t="inlineStr">
+      <c r="G3" s="44" t="n"/>
+      <c r="H3" s="44" t="n"/>
+      <c r="I3" s="47" t="n"/>
+      <c r="J3" s="43" t="inlineStr">
         <is>
           <t>Верхняя функция принадлежности</t>
         </is>
       </c>
-      <c r="K3" s="43" t="n"/>
-      <c r="L3" s="43" t="n"/>
-      <c r="M3" s="44" t="n"/>
-      <c r="N3" s="45" t="inlineStr">
+      <c r="K3" s="44" t="n"/>
+      <c r="L3" s="44" t="n"/>
+      <c r="M3" s="45" t="n"/>
+      <c r="N3" s="46" t="inlineStr">
         <is>
           <t>Нижняя функция принадлежности</t>
         </is>
       </c>
-      <c r="O3" s="43" t="n"/>
-      <c r="P3" s="43" t="n"/>
-      <c r="Q3" s="46" t="n"/>
-      <c r="R3" s="42" t="inlineStr">
+      <c r="O3" s="44" t="n"/>
+      <c r="P3" s="44" t="n"/>
+      <c r="Q3" s="47" t="n"/>
+      <c r="R3" s="43" t="inlineStr">
         <is>
           <t>Верхняя функция принадлежности</t>
         </is>
       </c>
-      <c r="S3" s="43" t="n"/>
-      <c r="T3" s="43" t="n"/>
-      <c r="U3" s="44" t="n"/>
-      <c r="V3" s="45" t="inlineStr">
+      <c r="S3" s="44" t="n"/>
+      <c r="T3" s="44" t="n"/>
+      <c r="U3" s="45" t="n"/>
+      <c r="V3" s="46" t="inlineStr">
         <is>
           <t>Нижняя функция принадлежности</t>
         </is>
       </c>
-      <c r="W3" s="43" t="n"/>
-      <c r="X3" s="43" t="n"/>
-      <c r="Y3" s="46" t="n"/>
-      <c r="Z3" s="42" t="inlineStr">
+      <c r="W3" s="44" t="n"/>
+      <c r="X3" s="44" t="n"/>
+      <c r="Y3" s="47" t="n"/>
+      <c r="Z3" s="43" t="inlineStr">
         <is>
           <t>Верхняя функция принадлежности</t>
         </is>
       </c>
-      <c r="AA3" s="43" t="n"/>
-      <c r="AB3" s="43" t="n"/>
-      <c r="AC3" s="44" t="n"/>
-      <c r="AD3" s="45" t="inlineStr">
+      <c r="AA3" s="44" t="n"/>
+      <c r="AB3" s="44" t="n"/>
+      <c r="AC3" s="45" t="n"/>
+      <c r="AD3" s="46" t="inlineStr">
         <is>
           <t>Нижняя функция принадлежности</t>
         </is>
       </c>
-      <c r="AE3" s="43" t="n"/>
-      <c r="AF3" s="43" t="n"/>
-      <c r="AG3" s="46" t="n"/>
+      <c r="AE3" s="44" t="n"/>
+      <c r="AF3" s="44" t="n"/>
+      <c r="AG3" s="47" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1989,704 +2011,1366 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q12"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="29" customWidth="1" min="11" max="11"/>
-    <col width="8" customWidth="1" min="12" max="12"/>
-    <col width="8" customWidth="1" min="13" max="13"/>
-    <col width="8" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="8" customWidth="1" min="16" max="16"/>
-    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="47" t="inlineStr">
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="48" t="inlineStr">
+        <is>
+          <t>Матрица взаимосвязанности функциональных требований</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="49" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B3" s="49" t="inlineStr">
+        <is>
+          <t>FR1</t>
+        </is>
+      </c>
+      <c r="C3" s="49" t="inlineStr">
+        <is>
+          <t>FR2</t>
+        </is>
+      </c>
+      <c r="D3" s="49" t="inlineStr">
+        <is>
+          <t>FR3</t>
+        </is>
+      </c>
+      <c r="E3" s="49" t="inlineStr">
+        <is>
+          <t>FR4</t>
+        </is>
+      </c>
+      <c r="F3" s="49" t="inlineStr">
+        <is>
+          <t>FR5</t>
+        </is>
+      </c>
+      <c r="G3" s="49" t="inlineStr">
+        <is>
+          <t>FR6</t>
+        </is>
+      </c>
+      <c r="H3" s="49" t="inlineStr">
+        <is>
+          <t>FR7</t>
+        </is>
+      </c>
+      <c r="I3" s="49" t="inlineStr">
+        <is>
+          <t>FR8</t>
+        </is>
+      </c>
+      <c r="J3" s="49" t="inlineStr">
+        <is>
+          <t>FR9</t>
+        </is>
+      </c>
+      <c r="K3" s="49" t="inlineStr">
+        <is>
+          <t>FR10</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="49" t="inlineStr">
+        <is>
+          <t>FR1</t>
+        </is>
+      </c>
+      <c r="B4" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="49" t="inlineStr">
+        <is>
+          <t>FR2</t>
+        </is>
+      </c>
+      <c r="B5" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="49" t="inlineStr">
+        <is>
+          <t>FR3</t>
+        </is>
+      </c>
+      <c r="B6" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="49" t="inlineStr">
+        <is>
+          <t>FR4</t>
+        </is>
+      </c>
+      <c r="B7" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="49" t="inlineStr">
+        <is>
+          <t>FR5</t>
+        </is>
+      </c>
+      <c r="B8" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="49" t="inlineStr">
+        <is>
+          <t>FR6</t>
+        </is>
+      </c>
+      <c r="B9" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="49" t="inlineStr">
+        <is>
+          <t>FR7</t>
+        </is>
+      </c>
+      <c r="B10" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="49" t="inlineStr">
+        <is>
+          <t>FR8</t>
+        </is>
+      </c>
+      <c r="B11" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" s="50" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="49" t="inlineStr">
+        <is>
+          <t>FR9</t>
+        </is>
+      </c>
+      <c r="B12" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" s="50" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="49" t="inlineStr">
+        <is>
+          <t>FR10</t>
+        </is>
+      </c>
+      <c r="B13" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" s="50" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="51" t="inlineStr">
+        <is>
+          <t>1) Итоговые нечеткие приоритеты и результаты дефаззификации</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="49" t="inlineStr">
         <is>
           <t>Приоритизация</t>
         </is>
       </c>
-      <c r="B1" s="47" t="inlineStr">
-        <is>
-          <t>Функциональное требование</t>
-        </is>
-      </c>
-      <c r="C1" s="47" t="inlineStr">
+      <c r="B2" s="49" t="inlineStr">
+        <is>
+          <t>Функциональное
+требование</t>
+        </is>
+      </c>
+      <c r="C2" s="49" t="inlineStr">
         <is>
           <t>RICE в формате ИНМТ2</t>
         </is>
       </c>
-      <c r="D1" s="47" t="n"/>
-      <c r="E1" s="47" t="n"/>
-      <c r="F1" s="47" t="n"/>
-      <c r="G1" s="47" t="n"/>
-      <c r="H1" s="47" t="n"/>
-      <c r="I1" s="47" t="n"/>
-      <c r="J1" s="47" t="n"/>
-      <c r="K1" s="47" t="inlineStr">
+      <c r="D2" s="49" t="n"/>
+      <c r="E2" s="49" t="n"/>
+      <c r="F2" s="49" t="n"/>
+      <c r="G2" s="49" t="n"/>
+      <c r="H2" s="49" t="n"/>
+      <c r="I2" s="49" t="n"/>
+      <c r="J2" s="49" t="n"/>
+      <c r="K2" s="49" t="inlineStr">
         <is>
           <t>RICE после редукции в ИНМТ1</t>
         </is>
       </c>
-      <c r="L1" s="47" t="n"/>
-      <c r="M1" s="47" t="n"/>
-      <c r="N1" s="47" t="n"/>
-      <c r="O1" s="47" t="inlineStr">
+      <c r="L2" s="49" t="n"/>
+      <c r="M2" s="49" t="n"/>
+      <c r="N2" s="49" t="n"/>
+      <c r="O2" s="49" t="inlineStr">
         <is>
           <t>Альфа-срез</t>
         </is>
       </c>
-      <c r="P1" s="47" t="n"/>
-      <c r="Q1" s="47" t="inlineStr">
+      <c r="P2" s="49" t="n"/>
+      <c r="Q2" s="49" t="inlineStr">
         <is>
           <t>Итог</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="24" customHeight="1">
-      <c r="A2" s="47" t="n"/>
-      <c r="B2" s="47" t="n"/>
-      <c r="C2" s="47" t="inlineStr">
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="49" t="n"/>
+      <c r="B3" s="49" t="n"/>
+      <c r="C3" s="49" t="inlineStr">
         <is>
           <t>x1</t>
         </is>
       </c>
-      <c r="D2" s="47" t="inlineStr">
+      <c r="D3" s="49" t="inlineStr">
         <is>
           <t>x2</t>
         </is>
       </c>
-      <c r="E2" s="47" t="inlineStr">
+      <c r="E3" s="49" t="inlineStr">
         <is>
           <t>x3</t>
         </is>
       </c>
-      <c r="F2" s="47" t="inlineStr">
+      <c r="F3" s="49" t="inlineStr">
         <is>
           <t>x4</t>
         </is>
       </c>
-      <c r="G2" s="47" t="inlineStr">
+      <c r="G3" s="49" t="inlineStr">
         <is>
           <t>x5</t>
         </is>
       </c>
-      <c r="H2" s="47" t="inlineStr">
+      <c r="H3" s="49" t="inlineStr">
         <is>
           <t>x6</t>
         </is>
       </c>
-      <c r="I2" s="47" t="inlineStr">
+      <c r="I3" s="49" t="inlineStr">
         <is>
           <t>x7</t>
         </is>
       </c>
-      <c r="J2" s="47" t="inlineStr">
+      <c r="J3" s="49" t="inlineStr">
         <is>
           <t>x8</t>
         </is>
       </c>
-      <c r="K2" s="47" t="inlineStr">
+      <c r="K3" s="49" t="inlineStr">
         <is>
           <t>x1</t>
         </is>
       </c>
-      <c r="L2" s="47" t="inlineStr">
+      <c r="L3" s="49" t="inlineStr">
         <is>
           <t>x2</t>
         </is>
       </c>
-      <c r="M2" s="47" t="inlineStr">
+      <c r="M3" s="49" t="inlineStr">
         <is>
           <t>x3</t>
         </is>
       </c>
-      <c r="N2" s="47" t="inlineStr">
+      <c r="N3" s="49" t="inlineStr">
         <is>
           <t>x4</t>
         </is>
       </c>
-      <c r="O2" s="47" t="inlineStr">
+      <c r="O3" s="49" t="inlineStr">
         <is>
           <t>Левый</t>
         </is>
       </c>
-      <c r="P2" s="47" t="inlineStr">
+      <c r="P3" s="49" t="inlineStr">
         <is>
           <t>Правый</t>
         </is>
       </c>
-      <c r="Q2" s="47" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="48" t="n">
+      <c r="Q3" s="49" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="48" t="inlineStr">
+      <c r="B4" s="52" t="inlineStr">
         <is>
           <t>FR1</t>
         </is>
       </c>
-      <c r="C3" s="48" t="n">
+      <c r="C4" s="53" t="n">
         <v>530.0700000000001</v>
       </c>
-      <c r="D3" s="48" t="n">
+      <c r="D4" s="53" t="n">
         <v>576.42</v>
       </c>
-      <c r="E3" s="48" t="n">
+      <c r="E4" s="53" t="n">
         <v>624.42</v>
       </c>
-      <c r="F3" s="48" t="n">
+      <c r="F4" s="53" t="n">
         <v>674.13</v>
       </c>
-      <c r="G3" s="48" t="n">
+      <c r="G4" s="53" t="n">
         <v>553.24</v>
       </c>
-      <c r="H3" s="48" t="n">
+      <c r="H4" s="53" t="n">
         <v>576.42</v>
       </c>
-      <c r="I3" s="48" t="n">
+      <c r="I4" s="53" t="n">
         <v>624.42</v>
       </c>
-      <c r="J3" s="48" t="n">
+      <c r="J4" s="53" t="n">
         <v>649.28</v>
       </c>
-      <c r="K3" s="48" t="n">
+      <c r="K4" s="53" t="n">
         <v>543.97</v>
       </c>
-      <c r="L3" s="48" t="n">
+      <c r="L4" s="53" t="n">
         <v>576.42</v>
       </c>
-      <c r="M3" s="48" t="n">
+      <c r="M4" s="53" t="n">
         <v>624.42</v>
       </c>
-      <c r="N3" s="48" t="n">
+      <c r="N4" s="53" t="n">
         <v>659.22</v>
       </c>
-      <c r="O3" s="48" t="n">
+      <c r="O4" s="53" t="n">
         <v>569.9299999999999</v>
       </c>
-      <c r="P3" s="48" t="n">
+      <c r="P4" s="53" t="n">
         <v>631.38</v>
       </c>
-      <c r="Q3" s="48" t="n">
+      <c r="Q4" s="53" t="n">
         <v>600.65</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="48" t="n">
+    <row r="5">
+      <c r="A5" s="50" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="48" t="inlineStr">
+      <c r="B5" s="52" t="inlineStr">
         <is>
           <t>FR9</t>
         </is>
       </c>
-      <c r="C4" s="48" t="n">
+      <c r="C5" s="53" t="n">
         <v>378.62</v>
       </c>
-      <c r="D4" s="48" t="n">
+      <c r="D5" s="53" t="n">
         <v>411.73</v>
       </c>
-      <c r="E4" s="48" t="n">
+      <c r="E5" s="53" t="n">
         <v>446.02</v>
       </c>
-      <c r="F4" s="48" t="n">
+      <c r="F5" s="53" t="n">
         <v>481.52</v>
       </c>
-      <c r="G4" s="48" t="n">
+      <c r="G5" s="53" t="n">
         <v>395.17</v>
       </c>
-      <c r="H4" s="48" t="n">
+      <c r="H5" s="53" t="n">
         <v>411.73</v>
       </c>
-      <c r="I4" s="48" t="n">
+      <c r="I5" s="53" t="n">
         <v>446.02</v>
       </c>
-      <c r="J4" s="48" t="n">
+      <c r="J5" s="53" t="n">
         <v>463.77</v>
       </c>
-      <c r="K4" s="48" t="n">
+      <c r="K5" s="53" t="n">
         <v>388.55</v>
       </c>
-      <c r="L4" s="48" t="n">
+      <c r="L5" s="53" t="n">
         <v>411.73</v>
       </c>
-      <c r="M4" s="48" t="n">
+      <c r="M5" s="53" t="n">
         <v>446.02</v>
       </c>
-      <c r="N4" s="48" t="n">
+      <c r="N5" s="53" t="n">
         <v>470.87</v>
       </c>
-      <c r="O4" s="48" t="n">
+      <c r="O5" s="53" t="n">
         <v>407.09</v>
       </c>
-      <c r="P4" s="48" t="n">
+      <c r="P5" s="53" t="n">
         <v>450.99</v>
       </c>
-      <c r="Q4" s="48" t="n">
+      <c r="Q5" s="53" t="n">
         <v>429.04</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="48" t="n">
+    <row r="6">
+      <c r="A6" s="50" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="48" t="inlineStr">
+      <c r="B6" s="52" t="inlineStr">
         <is>
           <t>FR3</t>
         </is>
       </c>
-      <c r="C5" s="48" t="n">
+      <c r="C6" s="53" t="n">
         <v>201.93</v>
       </c>
-      <c r="D5" s="48" t="n">
+      <c r="D6" s="53" t="n">
         <v>219.59</v>
       </c>
-      <c r="E5" s="48" t="n">
+      <c r="E6" s="53" t="n">
         <v>237.88</v>
       </c>
-      <c r="F5" s="48" t="n">
+      <c r="F6" s="53" t="n">
         <v>256.81</v>
       </c>
-      <c r="G5" s="48" t="n">
+      <c r="G6" s="53" t="n">
         <v>210.76</v>
       </c>
-      <c r="H5" s="48" t="n">
+      <c r="H6" s="53" t="n">
         <v>219.59</v>
       </c>
-      <c r="I5" s="48" t="n">
+      <c r="I6" s="53" t="n">
         <v>237.88</v>
       </c>
-      <c r="J5" s="48" t="n">
+      <c r="J6" s="53" t="n">
         <v>247.34</v>
       </c>
-      <c r="K5" s="48" t="n">
+      <c r="K6" s="53" t="n">
         <v>207.23</v>
       </c>
-      <c r="L5" s="48" t="n">
+      <c r="L6" s="53" t="n">
         <v>219.59</v>
       </c>
-      <c r="M5" s="48" t="n">
+      <c r="M6" s="53" t="n">
         <v>237.88</v>
       </c>
-      <c r="N5" s="48" t="n">
+      <c r="N6" s="53" t="n">
         <v>251.13</v>
       </c>
-      <c r="O5" s="48" t="n">
+      <c r="O6" s="53" t="n">
         <v>217.12</v>
       </c>
-      <c r="P5" s="48" t="n">
+      <c r="P6" s="53" t="n">
         <v>240.53</v>
       </c>
-      <c r="Q5" s="48" t="n">
+      <c r="Q6" s="53" t="n">
         <v>228.82</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="48" t="n">
+    <row r="7">
+      <c r="A7" s="50" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="48" t="inlineStr">
+      <c r="B7" s="52" t="inlineStr">
         <is>
           <t>FR10</t>
         </is>
       </c>
-      <c r="C6" s="48" t="n">
+      <c r="C7" s="53" t="n">
         <v>123.68</v>
       </c>
-      <c r="D6" s="48" t="n">
+      <c r="D7" s="53" t="n">
         <v>134.5</v>
       </c>
-      <c r="E6" s="48" t="n">
+      <c r="E7" s="53" t="n">
         <v>145.7</v>
       </c>
-      <c r="F6" s="48" t="n">
+      <c r="F7" s="53" t="n">
         <v>157.3</v>
       </c>
-      <c r="G6" s="48" t="n">
+      <c r="G7" s="53" t="n">
         <v>129.09</v>
       </c>
-      <c r="H6" s="48" t="n">
+      <c r="H7" s="53" t="n">
         <v>134.5</v>
       </c>
-      <c r="I6" s="48" t="n">
+      <c r="I7" s="53" t="n">
         <v>145.7</v>
       </c>
-      <c r="J6" s="48" t="n">
+      <c r="J7" s="53" t="n">
         <v>151.5</v>
       </c>
-      <c r="K6" s="48" t="n">
+      <c r="K7" s="53" t="n">
         <v>126.93</v>
       </c>
-      <c r="L6" s="48" t="n">
+      <c r="L7" s="53" t="n">
         <v>134.5</v>
       </c>
-      <c r="M6" s="48" t="n">
+      <c r="M7" s="53" t="n">
         <v>145.7</v>
       </c>
-      <c r="N6" s="48" t="n">
+      <c r="N7" s="53" t="n">
         <v>153.82</v>
       </c>
-      <c r="O6" s="48" t="n">
+      <c r="O7" s="53" t="n">
         <v>132.99</v>
       </c>
-      <c r="P6" s="48" t="n">
+      <c r="P7" s="53" t="n">
         <v>147.32</v>
       </c>
-      <c r="Q6" s="48" t="n">
+      <c r="Q7" s="53" t="n">
         <v>140.16</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="48" t="n">
+    <row r="8">
+      <c r="A8" s="50" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="48" t="inlineStr">
+      <c r="B8" s="52" t="inlineStr">
         <is>
           <t>FR8</t>
         </is>
       </c>
-      <c r="C7" s="48" t="n">
+      <c r="C8" s="53" t="n">
         <v>79.51000000000001</v>
       </c>
-      <c r="D7" s="48" t="n">
+      <c r="D8" s="53" t="n">
         <v>86.45999999999999</v>
       </c>
-      <c r="E7" s="48" t="n">
+      <c r="E8" s="53" t="n">
         <v>93.66</v>
       </c>
-      <c r="F7" s="48" t="n">
+      <c r="F8" s="53" t="n">
         <v>101.12</v>
       </c>
-      <c r="G7" s="48" t="n">
+      <c r="G8" s="53" t="n">
         <v>82.98999999999999</v>
       </c>
-      <c r="H7" s="48" t="n">
+      <c r="H8" s="53" t="n">
         <v>86.45999999999999</v>
       </c>
-      <c r="I7" s="48" t="n">
+      <c r="I8" s="53" t="n">
         <v>93.66</v>
       </c>
-      <c r="J7" s="48" t="n">
+      <c r="J8" s="53" t="n">
         <v>97.39</v>
       </c>
-      <c r="K7" s="48" t="n">
+      <c r="K8" s="53" t="n">
         <v>81.59999999999999</v>
       </c>
-      <c r="L7" s="48" t="n">
+      <c r="L8" s="53" t="n">
         <v>86.45999999999999</v>
       </c>
-      <c r="M7" s="48" t="n">
+      <c r="M8" s="53" t="n">
         <v>93.66</v>
       </c>
-      <c r="N7" s="48" t="n">
+      <c r="N8" s="53" t="n">
         <v>98.88</v>
       </c>
-      <c r="O7" s="48" t="n">
+      <c r="O8" s="53" t="n">
         <v>85.48999999999999</v>
       </c>
-      <c r="P7" s="48" t="n">
+      <c r="P8" s="53" t="n">
         <v>94.7</v>
       </c>
-      <c r="Q7" s="48" t="n">
+      <c r="Q8" s="53" t="n">
         <v>90.09</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="48" t="n">
+    <row r="9">
+      <c r="A9" s="50" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="48" t="inlineStr">
+      <c r="B9" s="52" t="inlineStr">
         <is>
           <t>FR2</t>
         </is>
       </c>
-      <c r="C8" s="48" t="n">
+      <c r="C9" s="53" t="n">
         <v>47.71</v>
       </c>
-      <c r="D8" s="48" t="n">
+      <c r="D9" s="53" t="n">
         <v>51.88</v>
       </c>
-      <c r="E8" s="48" t="n">
+      <c r="E9" s="53" t="n">
         <v>56.2</v>
       </c>
-      <c r="F8" s="48" t="n">
+      <c r="F9" s="53" t="n">
         <v>60.67</v>
       </c>
-      <c r="G8" s="48" t="n">
+      <c r="G9" s="53" t="n">
         <v>49.79</v>
       </c>
-      <c r="H8" s="48" t="n">
+      <c r="H9" s="53" t="n">
         <v>51.88</v>
       </c>
-      <c r="I8" s="48" t="n">
+      <c r="I9" s="53" t="n">
         <v>56.2</v>
       </c>
-      <c r="J8" s="48" t="n">
+      <c r="J9" s="53" t="n">
         <v>58.44</v>
       </c>
-      <c r="K8" s="48" t="n">
+      <c r="K9" s="53" t="n">
         <v>48.96</v>
       </c>
-      <c r="L8" s="48" t="n">
+      <c r="L9" s="53" t="n">
         <v>51.88</v>
       </c>
-      <c r="M8" s="48" t="n">
+      <c r="M9" s="53" t="n">
         <v>56.2</v>
       </c>
-      <c r="N8" s="48" t="n">
+      <c r="N9" s="53" t="n">
         <v>59.33</v>
       </c>
-      <c r="O8" s="48" t="n">
+      <c r="O9" s="53" t="n">
         <v>51.3</v>
       </c>
-      <c r="P8" s="48" t="n">
+      <c r="P9" s="53" t="n">
         <v>56.83</v>
       </c>
-      <c r="Q8" s="48" t="n">
+      <c r="Q9" s="53" t="n">
         <v>54.06</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="48" t="n">
+    <row r="10">
+      <c r="A10" s="50" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="48" t="inlineStr">
+      <c r="B10" s="52" t="inlineStr">
         <is>
           <t>FR5</t>
         </is>
       </c>
-      <c r="C9" s="48" t="n">
+      <c r="C10" s="53" t="n">
         <v>22.09</v>
       </c>
-      <c r="D9" s="48" t="n">
+      <c r="D10" s="53" t="n">
         <v>24.02</v>
       </c>
-      <c r="E9" s="48" t="n">
+      <c r="E10" s="53" t="n">
         <v>26.02</v>
       </c>
-      <c r="F9" s="48" t="n">
+      <c r="F10" s="53" t="n">
         <v>28.09</v>
       </c>
-      <c r="G9" s="48" t="n">
+      <c r="G10" s="53" t="n">
         <v>23.05</v>
       </c>
-      <c r="H9" s="48" t="n">
+      <c r="H10" s="53" t="n">
         <v>24.02</v>
       </c>
-      <c r="I9" s="48" t="n">
+      <c r="I10" s="53" t="n">
         <v>26.02</v>
       </c>
-      <c r="J9" s="48" t="n">
+      <c r="J10" s="53" t="n">
         <v>27.05</v>
       </c>
-      <c r="K9" s="48" t="n">
+      <c r="K10" s="53" t="n">
         <v>22.67</v>
       </c>
-      <c r="L9" s="48" t="n">
+      <c r="L10" s="53" t="n">
         <v>24.02</v>
       </c>
-      <c r="M9" s="48" t="n">
+      <c r="M10" s="53" t="n">
         <v>26.02</v>
       </c>
-      <c r="N9" s="48" t="n">
+      <c r="N10" s="53" t="n">
         <v>27.47</v>
       </c>
-      <c r="O9" s="48" t="n">
+      <c r="O10" s="53" t="n">
         <v>23.75</v>
       </c>
-      <c r="P9" s="48" t="n">
+      <c r="P10" s="53" t="n">
         <v>26.31</v>
       </c>
-      <c r="Q9" s="48" t="n">
+      <c r="Q10" s="53" t="n">
         <v>25.03</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="48" t="n">
+    <row r="11">
+      <c r="A11" s="50" t="n">
         <v>8</v>
       </c>
-      <c r="B10" s="48" t="inlineStr">
+      <c r="B11" s="52" t="inlineStr">
         <is>
           <t>FR4</t>
         </is>
       </c>
-      <c r="C10" s="48" t="n">
+      <c r="C11" s="53" t="n">
         <v>15.46</v>
       </c>
-      <c r="D10" s="48" t="n">
+      <c r="D11" s="53" t="n">
         <v>16.81</v>
       </c>
-      <c r="E10" s="48" t="n">
+      <c r="E11" s="53" t="n">
         <v>18.21</v>
       </c>
-      <c r="F10" s="48" t="n">
+      <c r="F11" s="53" t="n">
         <v>19.66</v>
       </c>
-      <c r="G10" s="48" t="n">
+      <c r="G11" s="53" t="n">
         <v>16.14</v>
       </c>
-      <c r="H10" s="48" t="n">
+      <c r="H11" s="53" t="n">
         <v>16.81</v>
       </c>
-      <c r="I10" s="48" t="n">
+      <c r="I11" s="53" t="n">
         <v>18.21</v>
       </c>
-      <c r="J10" s="48" t="n">
+      <c r="J11" s="53" t="n">
         <v>18.94</v>
       </c>
-      <c r="K10" s="48" t="n">
+      <c r="K11" s="53" t="n">
         <v>15.87</v>
       </c>
-      <c r="L10" s="48" t="n">
+      <c r="L11" s="53" t="n">
         <v>16.81</v>
       </c>
-      <c r="M10" s="48" t="n">
+      <c r="M11" s="53" t="n">
         <v>18.21</v>
       </c>
-      <c r="N10" s="48" t="n">
+      <c r="N11" s="53" t="n">
         <v>19.23</v>
       </c>
-      <c r="O10" s="48" t="n">
+      <c r="O11" s="53" t="n">
         <v>16.62</v>
       </c>
-      <c r="P10" s="48" t="n">
+      <c r="P11" s="53" t="n">
         <v>18.41</v>
       </c>
-      <c r="Q10" s="48" t="n">
+      <c r="Q11" s="53" t="n">
         <v>17.52</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="48" t="n">
+    <row r="12">
+      <c r="A12" s="50" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="48" t="inlineStr">
+      <c r="B12" s="52" t="inlineStr">
         <is>
           <t>FR7</t>
         </is>
       </c>
-      <c r="C11" s="48" t="n">
+      <c r="C12" s="53" t="n">
         <v>3.37</v>
       </c>
-      <c r="D11" s="48" t="n">
+      <c r="D12" s="53" t="n">
         <v>3.66</v>
       </c>
-      <c r="E11" s="48" t="n">
+      <c r="E12" s="53" t="n">
         <v>3.96</v>
       </c>
-      <c r="F11" s="48" t="n">
+      <c r="F12" s="53" t="n">
         <v>4.28</v>
       </c>
-      <c r="G11" s="48" t="n">
+      <c r="G12" s="53" t="n">
         <v>3.51</v>
       </c>
-      <c r="H11" s="48" t="n">
+      <c r="H12" s="53" t="n">
         <v>3.66</v>
       </c>
-      <c r="I11" s="48" t="n">
+      <c r="I12" s="53" t="n">
         <v>3.96</v>
       </c>
-      <c r="J11" s="48" t="n">
+      <c r="J12" s="53" t="n">
         <v>4.12</v>
       </c>
-      <c r="K11" s="48" t="n">
+      <c r="K12" s="53" t="n">
         <v>3.45</v>
       </c>
-      <c r="L11" s="48" t="n">
+      <c r="L12" s="53" t="n">
         <v>3.66</v>
       </c>
-      <c r="M11" s="48" t="n">
+      <c r="M12" s="53" t="n">
         <v>3.96</v>
       </c>
-      <c r="N11" s="48" t="n">
+      <c r="N12" s="53" t="n">
         <v>4.18</v>
       </c>
-      <c r="O11" s="48" t="n">
+      <c r="O12" s="53" t="n">
         <v>3.62</v>
       </c>
-      <c r="P11" s="48" t="n">
+      <c r="P12" s="53" t="n">
         <v>4</v>
       </c>
-      <c r="Q11" s="48" t="n">
+      <c r="Q12" s="53" t="n">
         <v>3.81</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="48" t="n">
+    <row r="13">
+      <c r="A13" s="50" t="n">
         <v>10</v>
       </c>
-      <c r="B12" s="48" t="inlineStr">
+      <c r="B13" s="52" t="inlineStr">
         <is>
           <t>FR6</t>
         </is>
       </c>
-      <c r="C12" s="48" t="n">
+      <c r="C13" s="53" t="n">
         <v>0.68</v>
       </c>
-      <c r="D12" s="48" t="n">
+      <c r="D13" s="53" t="n">
         <v>0.74</v>
       </c>
-      <c r="E12" s="48" t="n">
+      <c r="E13" s="53" t="n">
         <v>0.8</v>
       </c>
-      <c r="F12" s="48" t="n">
+      <c r="F13" s="53" t="n">
         <v>0.86</v>
       </c>
-      <c r="G12" s="48" t="n">
+      <c r="G13" s="53" t="n">
         <v>0.71</v>
       </c>
-      <c r="H12" s="48" t="n">
+      <c r="H13" s="53" t="n">
         <v>0.74</v>
       </c>
-      <c r="I12" s="48" t="n">
+      <c r="I13" s="53" t="n">
         <v>0.8</v>
       </c>
-      <c r="J12" s="48" t="n">
+      <c r="J13" s="53" t="n">
         <v>0.83</v>
       </c>
-      <c r="K12" s="48" t="n">
+      <c r="K13" s="53" t="n">
         <v>0.7</v>
       </c>
-      <c r="L12" s="48" t="n">
+      <c r="L13" s="53" t="n">
         <v>0.74</v>
       </c>
-      <c r="M12" s="48" t="n">
+      <c r="M13" s="53" t="n">
         <v>0.8</v>
       </c>
-      <c r="N12" s="48" t="n">
+      <c r="N13" s="53" t="n">
         <v>0.84</v>
       </c>
-      <c r="O12" s="48" t="n">
+      <c r="O13" s="53" t="n">
         <v>0.73</v>
       </c>
-      <c r="P12" s="48" t="n">
+      <c r="P13" s="53" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="Q12" s="48" t="n">
+      <c r="Q13" s="53" t="n">
         <v>0.77</v>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="51" t="inlineStr">
+        <is>
+          <t>2) Итоговая приоритизация после учета взаимосвязанности</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="36" customHeight="1">
+      <c r="A17" s="49" t="inlineStr">
+        <is>
+          <t>Место</t>
+        </is>
+      </c>
+      <c r="B17" s="49" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="C17" s="49" t="inlineStr">
+        <is>
+          <t>Исходный центроид</t>
+        </is>
+      </c>
+      <c r="D17" s="49" t="inlineStr">
+        <is>
+          <t>Скорректированный
+центроид</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="B18" s="52" t="inlineStr">
+        <is>
+          <t>FR1</t>
+        </is>
+      </c>
+      <c r="C18" s="53" t="n">
+        <v>600.65</v>
+      </c>
+      <c r="D18" s="53" t="n">
+        <v>600.65</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="B19" s="52" t="inlineStr">
+        <is>
+          <t>FR4</t>
+        </is>
+      </c>
+      <c r="C19" s="53" t="n">
+        <v>17.52</v>
+      </c>
+      <c r="D19" s="53" t="n">
+        <v>600.65</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="50" t="n">
+        <v>3</v>
+      </c>
+      <c r="B20" s="52" t="inlineStr">
+        <is>
+          <t>FR9</t>
+        </is>
+      </c>
+      <c r="C20" s="53" t="n">
+        <v>429.04</v>
+      </c>
+      <c r="D20" s="53" t="n">
+        <v>429.04</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="50" t="n">
+        <v>4</v>
+      </c>
+      <c r="B21" s="52" t="inlineStr">
+        <is>
+          <t>FR10</t>
+        </is>
+      </c>
+      <c r="C21" s="53" t="n">
+        <v>140.16</v>
+      </c>
+      <c r="D21" s="53" t="n">
+        <v>429.04</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="50" t="n">
+        <v>5</v>
+      </c>
+      <c r="B22" s="52" t="inlineStr">
+        <is>
+          <t>FR8</t>
+        </is>
+      </c>
+      <c r="C22" s="53" t="n">
+        <v>90.09</v>
+      </c>
+      <c r="D22" s="53" t="n">
+        <v>429.04</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="50" t="n">
+        <v>6</v>
+      </c>
+      <c r="B23" s="52" t="inlineStr">
+        <is>
+          <t>FR3</t>
+        </is>
+      </c>
+      <c r="C23" s="53" t="n">
+        <v>228.82</v>
+      </c>
+      <c r="D23" s="53" t="n">
+        <v>228.82</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="50" t="n">
+        <v>7</v>
+      </c>
+      <c r="B24" s="52" t="inlineStr">
+        <is>
+          <t>FR2</t>
+        </is>
+      </c>
+      <c r="C24" s="53" t="n">
+        <v>54.06</v>
+      </c>
+      <c r="D24" s="53" t="n">
+        <v>54.06</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="50" t="n">
+        <v>8</v>
+      </c>
+      <c r="B25" s="52" t="inlineStr">
+        <is>
+          <t>FR5</t>
+        </is>
+      </c>
+      <c r="C25" s="53" t="n">
+        <v>25.03</v>
+      </c>
+      <c r="D25" s="53" t="n">
+        <v>25.03</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="50" t="n">
+        <v>9</v>
+      </c>
+      <c r="B26" s="52" t="inlineStr">
+        <is>
+          <t>FR7</t>
+        </is>
+      </c>
+      <c r="C26" s="53" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="D26" s="53" t="n">
+        <v>3.81</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="50" t="n">
+        <v>10</v>
+      </c>
+      <c r="B27" s="52" t="inlineStr">
+        <is>
+          <t>FR6</t>
+        </is>
+      </c>
+      <c r="C27" s="53" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="D27" s="53" t="n">
+        <v>3.81</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="C1:J1"/>
-    <mergeCell ref="Q1:Q2"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="O2:P2"/>
+    <mergeCell ref="C2:J2"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="Q2:Q3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/2026.02.16_Файлы загрузки и выгрузки данных/Итоги_Fuzzy RICE_один эксперт.xlsx
+++ b/2026.02.16_Файлы загрузки и выгрузки данных/Итоги_Fuzzy RICE_один эксперт.xlsx
@@ -316,6 +316,36 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top style="medium">
@@ -352,36 +382,6 @@
         <color indexed="64"/>
       </right>
       <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
         <color indexed="64"/>
       </top>
       <bottom style="thin">
@@ -399,7 +399,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -431,7 +431,15 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -447,24 +455,19 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -834,129 +837,129 @@
   <sheetData>
     <row r="1" ht="15.75" customHeight="1" thickBot="1"/>
     <row r="2">
-      <c r="A2" s="31" t="inlineStr">
+      <c r="A2" s="39" t="inlineStr">
         <is>
           <t>Feature</t>
         </is>
       </c>
-      <c r="B2" s="37" t="inlineStr">
+      <c r="B2" s="31" t="inlineStr">
         <is>
           <t>R, Reach (Охват), количество человек</t>
         </is>
       </c>
-      <c r="C2" s="40" t="n"/>
-      <c r="D2" s="40" t="n"/>
-      <c r="E2" s="40" t="n"/>
-      <c r="F2" s="40" t="n"/>
-      <c r="G2" s="40" t="n"/>
-      <c r="H2" s="40" t="n"/>
-      <c r="I2" s="41" t="n"/>
-      <c r="J2" s="37" t="inlineStr">
+      <c r="C2" s="41" t="n"/>
+      <c r="D2" s="41" t="n"/>
+      <c r="E2" s="41" t="n"/>
+      <c r="F2" s="41" t="n"/>
+      <c r="G2" s="41" t="n"/>
+      <c r="H2" s="41" t="n"/>
+      <c r="I2" s="42" t="n"/>
+      <c r="J2" s="31" t="inlineStr">
         <is>
           <t>I, Impact (Влияние), оценка в баллах</t>
         </is>
       </c>
-      <c r="K2" s="40" t="n"/>
-      <c r="L2" s="40" t="n"/>
-      <c r="M2" s="40" t="n"/>
-      <c r="N2" s="40" t="n"/>
-      <c r="O2" s="40" t="n"/>
-      <c r="P2" s="40" t="n"/>
-      <c r="Q2" s="41" t="n"/>
-      <c r="R2" s="37" t="inlineStr">
+      <c r="K2" s="41" t="n"/>
+      <c r="L2" s="41" t="n"/>
+      <c r="M2" s="41" t="n"/>
+      <c r="N2" s="41" t="n"/>
+      <c r="O2" s="41" t="n"/>
+      <c r="P2" s="41" t="n"/>
+      <c r="Q2" s="42" t="n"/>
+      <c r="R2" s="31" t="inlineStr">
         <is>
           <t>С, Confidence (Уверенность), коэффициент от 0,5 до 1</t>
         </is>
       </c>
-      <c r="S2" s="40" t="n"/>
-      <c r="T2" s="40" t="n"/>
-      <c r="U2" s="40" t="n"/>
-      <c r="V2" s="40" t="n"/>
-      <c r="W2" s="40" t="n"/>
-      <c r="X2" s="40" t="n"/>
-      <c r="Y2" s="41" t="n"/>
-      <c r="Z2" s="37" t="inlineStr">
+      <c r="S2" s="41" t="n"/>
+      <c r="T2" s="41" t="n"/>
+      <c r="U2" s="41" t="n"/>
+      <c r="V2" s="41" t="n"/>
+      <c r="W2" s="41" t="n"/>
+      <c r="X2" s="41" t="n"/>
+      <c r="Y2" s="42" t="n"/>
+      <c r="Z2" s="31" t="inlineStr">
         <is>
           <t>E, Effort (Трудозатраты), количество недель</t>
         </is>
       </c>
-      <c r="AA2" s="40" t="n"/>
-      <c r="AB2" s="40" t="n"/>
-      <c r="AC2" s="40" t="n"/>
-      <c r="AD2" s="40" t="n"/>
-      <c r="AE2" s="40" t="n"/>
-      <c r="AF2" s="40" t="n"/>
-      <c r="AG2" s="41" t="n"/>
+      <c r="AA2" s="41" t="n"/>
+      <c r="AB2" s="41" t="n"/>
+      <c r="AC2" s="41" t="n"/>
+      <c r="AD2" s="41" t="n"/>
+      <c r="AE2" s="41" t="n"/>
+      <c r="AF2" s="41" t="n"/>
+      <c r="AG2" s="42" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="42" t="n"/>
-      <c r="B3" s="43" t="inlineStr">
+      <c r="A3" s="43" t="n"/>
+      <c r="B3" s="44" t="inlineStr">
         <is>
           <t>Верхняя функция принадлежности</t>
         </is>
       </c>
-      <c r="C3" s="44" t="n"/>
-      <c r="D3" s="44" t="n"/>
-      <c r="E3" s="45" t="n"/>
-      <c r="F3" s="46" t="inlineStr">
+      <c r="C3" s="45" t="n"/>
+      <c r="D3" s="45" t="n"/>
+      <c r="E3" s="46" t="n"/>
+      <c r="F3" s="47" t="inlineStr">
         <is>
           <t>Нижняя функция принадлежности</t>
         </is>
       </c>
-      <c r="G3" s="44" t="n"/>
-      <c r="H3" s="44" t="n"/>
-      <c r="I3" s="47" t="n"/>
-      <c r="J3" s="43" t="inlineStr">
+      <c r="G3" s="45" t="n"/>
+      <c r="H3" s="45" t="n"/>
+      <c r="I3" s="48" t="n"/>
+      <c r="J3" s="44" t="inlineStr">
         <is>
           <t>Верхняя функция принадлежности</t>
         </is>
       </c>
-      <c r="K3" s="44" t="n"/>
-      <c r="L3" s="44" t="n"/>
-      <c r="M3" s="45" t="n"/>
-      <c r="N3" s="46" t="inlineStr">
+      <c r="K3" s="45" t="n"/>
+      <c r="L3" s="45" t="n"/>
+      <c r="M3" s="46" t="n"/>
+      <c r="N3" s="47" t="inlineStr">
         <is>
           <t>Нижняя функция принадлежности</t>
         </is>
       </c>
-      <c r="O3" s="44" t="n"/>
-      <c r="P3" s="44" t="n"/>
-      <c r="Q3" s="47" t="n"/>
-      <c r="R3" s="43" t="inlineStr">
+      <c r="O3" s="45" t="n"/>
+      <c r="P3" s="45" t="n"/>
+      <c r="Q3" s="48" t="n"/>
+      <c r="R3" s="44" t="inlineStr">
         <is>
           <t>Верхняя функция принадлежности</t>
         </is>
       </c>
-      <c r="S3" s="44" t="n"/>
-      <c r="T3" s="44" t="n"/>
-      <c r="U3" s="45" t="n"/>
-      <c r="V3" s="46" t="inlineStr">
+      <c r="S3" s="45" t="n"/>
+      <c r="T3" s="45" t="n"/>
+      <c r="U3" s="46" t="n"/>
+      <c r="V3" s="47" t="inlineStr">
         <is>
           <t>Нижняя функция принадлежности</t>
         </is>
       </c>
-      <c r="W3" s="44" t="n"/>
-      <c r="X3" s="44" t="n"/>
-      <c r="Y3" s="47" t="n"/>
-      <c r="Z3" s="43" t="inlineStr">
+      <c r="W3" s="45" t="n"/>
+      <c r="X3" s="45" t="n"/>
+      <c r="Y3" s="48" t="n"/>
+      <c r="Z3" s="44" t="inlineStr">
         <is>
           <t>Верхняя функция принадлежности</t>
         </is>
       </c>
-      <c r="AA3" s="44" t="n"/>
-      <c r="AB3" s="44" t="n"/>
-      <c r="AC3" s="45" t="n"/>
-      <c r="AD3" s="46" t="inlineStr">
+      <c r="AA3" s="45" t="n"/>
+      <c r="AB3" s="45" t="n"/>
+      <c r="AC3" s="46" t="n"/>
+      <c r="AD3" s="47" t="inlineStr">
         <is>
           <t>Нижняя функция принадлежности</t>
         </is>
       </c>
-      <c r="AE3" s="44" t="n"/>
-      <c r="AF3" s="44" t="n"/>
-      <c r="AG3" s="47" t="n"/>
+      <c r="AE3" s="45" t="n"/>
+      <c r="AF3" s="45" t="n"/>
+      <c r="AG3" s="48" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="40" t="inlineStr">
         <is>
           <t>FR1</t>
         </is>
@@ -1059,7 +1062,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="40" t="inlineStr">
         <is>
           <t>FR2</t>
         </is>
@@ -1162,7 +1165,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="40" t="inlineStr">
         <is>
           <t>FR3</t>
         </is>
@@ -1265,7 +1268,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="40" t="inlineStr">
         <is>
           <t>FR4</t>
         </is>
@@ -1368,7 +1371,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="40" t="inlineStr">
         <is>
           <t>FR5</t>
         </is>
@@ -1471,7 +1474,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="40" t="inlineStr">
         <is>
           <t>FR6</t>
         </is>
@@ -1574,7 +1577,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="40" t="inlineStr">
         <is>
           <t>FR7</t>
         </is>
@@ -1677,7 +1680,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="40" t="inlineStr">
         <is>
           <t>FR8</t>
         </is>
@@ -1780,7 +1783,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="40" t="inlineStr">
         <is>
           <t>FR9</t>
         </is>
@@ -1883,7 +1886,7 @@
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="40" t="inlineStr">
         <is>
           <t>FR10</t>
         </is>
@@ -1992,14 +1995,14 @@
     <mergeCell ref="Z2:AG2"/>
     <mergeCell ref="Z3:AC3"/>
     <mergeCell ref="F3:I3"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="J3:M3"/>
     <mergeCell ref="AD3:AG3"/>
-    <mergeCell ref="J3:M3"/>
-    <mergeCell ref="B2:I2"/>
     <mergeCell ref="N3:Q3"/>
     <mergeCell ref="R2:Y2"/>
     <mergeCell ref="J2:Q2"/>
+    <mergeCell ref="A2:A3"/>
     <mergeCell ref="B3:E3"/>
-    <mergeCell ref="A2:A3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2028,7 +2031,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="48" t="inlineStr">
+      <c r="A1" s="49" t="inlineStr">
         <is>
           <t>Матрица взаимосвязанности функциональных требований</t>
         </is>
@@ -2036,429 +2039,429 @@
     </row>
     <row r="2"/>
     <row r="3">
-      <c r="A3" s="49" t="inlineStr">
+      <c r="A3" s="50" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="B3" s="49" t="inlineStr">
+      <c r="B3" s="50" t="inlineStr">
         <is>
           <t>FR1</t>
         </is>
       </c>
-      <c r="C3" s="49" t="inlineStr">
+      <c r="C3" s="50" t="inlineStr">
         <is>
           <t>FR2</t>
         </is>
       </c>
-      <c r="D3" s="49" t="inlineStr">
+      <c r="D3" s="50" t="inlineStr">
         <is>
           <t>FR3</t>
         </is>
       </c>
-      <c r="E3" s="49" t="inlineStr">
+      <c r="E3" s="50" t="inlineStr">
         <is>
           <t>FR4</t>
         </is>
       </c>
-      <c r="F3" s="49" t="inlineStr">
+      <c r="F3" s="50" t="inlineStr">
         <is>
           <t>FR5</t>
         </is>
       </c>
-      <c r="G3" s="49" t="inlineStr">
+      <c r="G3" s="50" t="inlineStr">
         <is>
           <t>FR6</t>
         </is>
       </c>
-      <c r="H3" s="49" t="inlineStr">
+      <c r="H3" s="50" t="inlineStr">
         <is>
           <t>FR7</t>
         </is>
       </c>
-      <c r="I3" s="49" t="inlineStr">
+      <c r="I3" s="50" t="inlineStr">
         <is>
           <t>FR8</t>
         </is>
       </c>
-      <c r="J3" s="49" t="inlineStr">
+      <c r="J3" s="50" t="inlineStr">
         <is>
           <t>FR9</t>
         </is>
       </c>
-      <c r="K3" s="49" t="inlineStr">
+      <c r="K3" s="50" t="inlineStr">
         <is>
           <t>FR10</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="49" t="inlineStr">
+      <c r="A4" s="50" t="inlineStr">
         <is>
           <t>FR1</t>
         </is>
       </c>
-      <c r="B4" s="50" t="n">
+      <c r="B4" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" s="50" t="n">
+      <c r="C4" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="F4" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" s="50" t="n">
+      <c r="F4" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="51" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="49" t="inlineStr">
+      <c r="A5" s="50" t="inlineStr">
         <is>
           <t>FR2</t>
         </is>
       </c>
-      <c r="B5" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" s="50" t="n">
+      <c r="B5" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="D5" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" s="50" t="n">
+      <c r="D5" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="51" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="49" t="inlineStr">
+      <c r="A6" s="50" t="inlineStr">
         <is>
           <t>FR3</t>
         </is>
       </c>
-      <c r="B6" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="50" t="n">
+      <c r="B6" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="E6" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" s="50" t="n">
+      <c r="E6" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="51" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="49" t="inlineStr">
+      <c r="A7" s="50" t="inlineStr">
         <is>
           <t>FR4</t>
         </is>
       </c>
-      <c r="B7" s="50" t="n">
+      <c r="B7" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="50" t="n">
+      <c r="C7" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="F7" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" s="50" t="n">
+      <c r="F7" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="51" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="49" t="inlineStr">
+      <c r="A8" s="50" t="inlineStr">
         <is>
           <t>FR5</t>
         </is>
       </c>
-      <c r="B8" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="50" t="n">
+      <c r="B8" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="G8" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" s="50" t="n">
+      <c r="G8" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="51" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="49" t="inlineStr">
+      <c r="A9" s="50" t="inlineStr">
         <is>
           <t>FR6</t>
         </is>
       </c>
-      <c r="B9" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="50" t="n">
+      <c r="B9" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="H9" s="50" t="n">
+      <c r="H9" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="I9" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" s="50" t="n">
+      <c r="I9" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="51" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="49" t="inlineStr">
+      <c r="A10" s="50" t="inlineStr">
         <is>
           <t>FR7</t>
         </is>
       </c>
-      <c r="B10" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="50" t="n">
+      <c r="B10" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="H10" s="50" t="n">
+      <c r="H10" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="I10" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" s="50" t="n">
+      <c r="I10" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="51" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="49" t="inlineStr">
+      <c r="A11" s="50" t="inlineStr">
         <is>
           <t>FR8</t>
         </is>
       </c>
-      <c r="B11" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="50" t="n">
+      <c r="B11" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="J11" s="50" t="n">
+      <c r="J11" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="K11" s="50" t="n">
+      <c r="K11" s="51" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="49" t="inlineStr">
+      <c r="A12" s="50" t="inlineStr">
         <is>
           <t>FR9</t>
         </is>
       </c>
-      <c r="B12" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="50" t="n">
+      <c r="B12" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="J12" s="50" t="n">
+      <c r="J12" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="K12" s="50" t="n">
+      <c r="K12" s="51" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="49" t="inlineStr">
+      <c r="A13" s="50" t="inlineStr">
         <is>
           <t>FR10</t>
         </is>
       </c>
-      <c r="B13" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="50" t="n">
+      <c r="B13" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="J13" s="50" t="n">
+      <c r="J13" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="K13" s="50" t="n">
+      <c r="K13" s="51" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2496,707 +2499,707 @@
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="51" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>1) Итоговые нечеткие приоритеты и результаты дефаззификации</t>
         </is>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1">
-      <c r="A2" s="49" t="inlineStr">
+      <c r="A2" s="50" t="inlineStr">
         <is>
           <t>Приоритизация</t>
         </is>
       </c>
-      <c r="B2" s="49" t="inlineStr">
+      <c r="B2" s="50" t="inlineStr">
         <is>
           <t>Функциональное
 требование</t>
         </is>
       </c>
-      <c r="C2" s="49" t="inlineStr">
+      <c r="C2" s="50" t="inlineStr">
         <is>
           <t>RICE в формате ИНМТ2</t>
         </is>
       </c>
-      <c r="D2" s="49" t="n"/>
-      <c r="E2" s="49" t="n"/>
-      <c r="F2" s="49" t="n"/>
-      <c r="G2" s="49" t="n"/>
-      <c r="H2" s="49" t="n"/>
-      <c r="I2" s="49" t="n"/>
-      <c r="J2" s="49" t="n"/>
-      <c r="K2" s="49" t="inlineStr">
+      <c r="D2" s="50" t="n"/>
+      <c r="E2" s="50" t="n"/>
+      <c r="F2" s="50" t="n"/>
+      <c r="G2" s="50" t="n"/>
+      <c r="H2" s="50" t="n"/>
+      <c r="I2" s="50" t="n"/>
+      <c r="J2" s="50" t="n"/>
+      <c r="K2" s="50" t="inlineStr">
         <is>
           <t>RICE после редукции в ИНМТ1</t>
         </is>
       </c>
-      <c r="L2" s="49" t="n"/>
-      <c r="M2" s="49" t="n"/>
-      <c r="N2" s="49" t="n"/>
-      <c r="O2" s="49" t="inlineStr">
+      <c r="L2" s="50" t="n"/>
+      <c r="M2" s="50" t="n"/>
+      <c r="N2" s="50" t="n"/>
+      <c r="O2" s="50" t="inlineStr">
         <is>
           <t>Альфа-срез</t>
         </is>
       </c>
-      <c r="P2" s="49" t="n"/>
-      <c r="Q2" s="49" t="inlineStr">
+      <c r="P2" s="50" t="n"/>
+      <c r="Q2" s="50" t="inlineStr">
         <is>
           <t>Итог</t>
         </is>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="49" t="n"/>
-      <c r="B3" s="49" t="n"/>
-      <c r="C3" s="49" t="inlineStr">
+      <c r="A3" s="50" t="n"/>
+      <c r="B3" s="50" t="n"/>
+      <c r="C3" s="50" t="inlineStr">
         <is>
           <t>x1</t>
         </is>
       </c>
-      <c r="D3" s="49" t="inlineStr">
+      <c r="D3" s="50" t="inlineStr">
         <is>
           <t>x2</t>
         </is>
       </c>
-      <c r="E3" s="49" t="inlineStr">
+      <c r="E3" s="50" t="inlineStr">
         <is>
           <t>x3</t>
         </is>
       </c>
-      <c r="F3" s="49" t="inlineStr">
+      <c r="F3" s="50" t="inlineStr">
         <is>
           <t>x4</t>
         </is>
       </c>
-      <c r="G3" s="49" t="inlineStr">
+      <c r="G3" s="50" t="inlineStr">
         <is>
           <t>x5</t>
         </is>
       </c>
-      <c r="H3" s="49" t="inlineStr">
+      <c r="H3" s="50" t="inlineStr">
         <is>
           <t>x6</t>
         </is>
       </c>
-      <c r="I3" s="49" t="inlineStr">
+      <c r="I3" s="50" t="inlineStr">
         <is>
           <t>x7</t>
         </is>
       </c>
-      <c r="J3" s="49" t="inlineStr">
+      <c r="J3" s="50" t="inlineStr">
         <is>
           <t>x8</t>
         </is>
       </c>
-      <c r="K3" s="49" t="inlineStr">
+      <c r="K3" s="50" t="inlineStr">
         <is>
           <t>x1</t>
         </is>
       </c>
-      <c r="L3" s="49" t="inlineStr">
+      <c r="L3" s="50" t="inlineStr">
         <is>
           <t>x2</t>
         </is>
       </c>
-      <c r="M3" s="49" t="inlineStr">
+      <c r="M3" s="50" t="inlineStr">
         <is>
           <t>x3</t>
         </is>
       </c>
-      <c r="N3" s="49" t="inlineStr">
+      <c r="N3" s="50" t="inlineStr">
         <is>
           <t>x4</t>
         </is>
       </c>
-      <c r="O3" s="49" t="inlineStr">
+      <c r="O3" s="50" t="inlineStr">
         <is>
           <t>Левый</t>
         </is>
       </c>
-      <c r="P3" s="49" t="inlineStr">
+      <c r="P3" s="50" t="inlineStr">
         <is>
           <t>Правый</t>
         </is>
       </c>
-      <c r="Q3" s="49" t="n"/>
+      <c r="Q3" s="50" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="50" t="n">
+      <c r="A4" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="52" t="inlineStr">
+      <c r="B4" s="53" t="inlineStr">
         <is>
           <t>FR1</t>
         </is>
       </c>
-      <c r="C4" s="53" t="n">
+      <c r="C4" s="54" t="n">
         <v>530.0700000000001</v>
       </c>
-      <c r="D4" s="53" t="n">
+      <c r="D4" s="54" t="n">
         <v>576.42</v>
       </c>
-      <c r="E4" s="53" t="n">
+      <c r="E4" s="54" t="n">
         <v>624.42</v>
       </c>
-      <c r="F4" s="53" t="n">
+      <c r="F4" s="54" t="n">
         <v>674.13</v>
       </c>
-      <c r="G4" s="53" t="n">
+      <c r="G4" s="54" t="n">
         <v>553.24</v>
       </c>
-      <c r="H4" s="53" t="n">
+      <c r="H4" s="54" t="n">
         <v>576.42</v>
       </c>
-      <c r="I4" s="53" t="n">
+      <c r="I4" s="54" t="n">
         <v>624.42</v>
       </c>
-      <c r="J4" s="53" t="n">
+      <c r="J4" s="54" t="n">
         <v>649.28</v>
       </c>
-      <c r="K4" s="53" t="n">
+      <c r="K4" s="54" t="n">
         <v>543.97</v>
       </c>
-      <c r="L4" s="53" t="n">
+      <c r="L4" s="54" t="n">
         <v>576.42</v>
       </c>
-      <c r="M4" s="53" t="n">
+      <c r="M4" s="54" t="n">
         <v>624.42</v>
       </c>
-      <c r="N4" s="53" t="n">
+      <c r="N4" s="54" t="n">
         <v>659.22</v>
       </c>
-      <c r="O4" s="53" t="n">
+      <c r="O4" s="54" t="n">
         <v>569.9299999999999</v>
       </c>
-      <c r="P4" s="53" t="n">
+      <c r="P4" s="54" t="n">
         <v>631.38</v>
       </c>
-      <c r="Q4" s="53" t="n">
+      <c r="Q4" s="54" t="n">
         <v>600.65</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="50" t="n">
+      <c r="A5" s="51" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="52" t="inlineStr">
+      <c r="B5" s="53" t="inlineStr">
         <is>
           <t>FR9</t>
         </is>
       </c>
-      <c r="C5" s="53" t="n">
+      <c r="C5" s="54" t="n">
         <v>378.62</v>
       </c>
-      <c r="D5" s="53" t="n">
+      <c r="D5" s="54" t="n">
         <v>411.73</v>
       </c>
-      <c r="E5" s="53" t="n">
+      <c r="E5" s="54" t="n">
         <v>446.02</v>
       </c>
-      <c r="F5" s="53" t="n">
+      <c r="F5" s="54" t="n">
         <v>481.52</v>
       </c>
-      <c r="G5" s="53" t="n">
+      <c r="G5" s="54" t="n">
         <v>395.17</v>
       </c>
-      <c r="H5" s="53" t="n">
+      <c r="H5" s="54" t="n">
         <v>411.73</v>
       </c>
-      <c r="I5" s="53" t="n">
+      <c r="I5" s="54" t="n">
         <v>446.02</v>
       </c>
-      <c r="J5" s="53" t="n">
+      <c r="J5" s="54" t="n">
         <v>463.77</v>
       </c>
-      <c r="K5" s="53" t="n">
+      <c r="K5" s="54" t="n">
         <v>388.55</v>
       </c>
-      <c r="L5" s="53" t="n">
+      <c r="L5" s="54" t="n">
         <v>411.73</v>
       </c>
-      <c r="M5" s="53" t="n">
+      <c r="M5" s="54" t="n">
         <v>446.02</v>
       </c>
-      <c r="N5" s="53" t="n">
+      <c r="N5" s="54" t="n">
         <v>470.87</v>
       </c>
-      <c r="O5" s="53" t="n">
+      <c r="O5" s="54" t="n">
         <v>407.09</v>
       </c>
-      <c r="P5" s="53" t="n">
+      <c r="P5" s="54" t="n">
         <v>450.99</v>
       </c>
-      <c r="Q5" s="53" t="n">
+      <c r="Q5" s="54" t="n">
         <v>429.04</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="50" t="n">
+      <c r="A6" s="51" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="52" t="inlineStr">
+      <c r="B6" s="53" t="inlineStr">
         <is>
           <t>FR3</t>
         </is>
       </c>
-      <c r="C6" s="53" t="n">
+      <c r="C6" s="54" t="n">
         <v>201.93</v>
       </c>
-      <c r="D6" s="53" t="n">
+      <c r="D6" s="54" t="n">
         <v>219.59</v>
       </c>
-      <c r="E6" s="53" t="n">
+      <c r="E6" s="54" t="n">
         <v>237.88</v>
       </c>
-      <c r="F6" s="53" t="n">
+      <c r="F6" s="54" t="n">
         <v>256.81</v>
       </c>
-      <c r="G6" s="53" t="n">
+      <c r="G6" s="54" t="n">
         <v>210.76</v>
       </c>
-      <c r="H6" s="53" t="n">
+      <c r="H6" s="54" t="n">
         <v>219.59</v>
       </c>
-      <c r="I6" s="53" t="n">
+      <c r="I6" s="54" t="n">
         <v>237.88</v>
       </c>
-      <c r="J6" s="53" t="n">
+      <c r="J6" s="54" t="n">
         <v>247.34</v>
       </c>
-      <c r="K6" s="53" t="n">
+      <c r="K6" s="54" t="n">
         <v>207.23</v>
       </c>
-      <c r="L6" s="53" t="n">
+      <c r="L6" s="54" t="n">
         <v>219.59</v>
       </c>
-      <c r="M6" s="53" t="n">
+      <c r="M6" s="54" t="n">
         <v>237.88</v>
       </c>
-      <c r="N6" s="53" t="n">
+      <c r="N6" s="54" t="n">
         <v>251.13</v>
       </c>
-      <c r="O6" s="53" t="n">
+      <c r="O6" s="54" t="n">
         <v>217.12</v>
       </c>
-      <c r="P6" s="53" t="n">
+      <c r="P6" s="54" t="n">
         <v>240.53</v>
       </c>
-      <c r="Q6" s="53" t="n">
+      <c r="Q6" s="54" t="n">
         <v>228.82</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="50" t="n">
+      <c r="A7" s="51" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="52" t="inlineStr">
+      <c r="B7" s="53" t="inlineStr">
         <is>
           <t>FR10</t>
         </is>
       </c>
-      <c r="C7" s="53" t="n">
+      <c r="C7" s="54" t="n">
         <v>123.68</v>
       </c>
-      <c r="D7" s="53" t="n">
+      <c r="D7" s="54" t="n">
         <v>134.5</v>
       </c>
-      <c r="E7" s="53" t="n">
+      <c r="E7" s="54" t="n">
         <v>145.7</v>
       </c>
-      <c r="F7" s="53" t="n">
+      <c r="F7" s="54" t="n">
         <v>157.3</v>
       </c>
-      <c r="G7" s="53" t="n">
+      <c r="G7" s="54" t="n">
         <v>129.09</v>
       </c>
-      <c r="H7" s="53" t="n">
+      <c r="H7" s="54" t="n">
         <v>134.5</v>
       </c>
-      <c r="I7" s="53" t="n">
+      <c r="I7" s="54" t="n">
         <v>145.7</v>
       </c>
-      <c r="J7" s="53" t="n">
+      <c r="J7" s="54" t="n">
         <v>151.5</v>
       </c>
-      <c r="K7" s="53" t="n">
+      <c r="K7" s="54" t="n">
         <v>126.93</v>
       </c>
-      <c r="L7" s="53" t="n">
+      <c r="L7" s="54" t="n">
         <v>134.5</v>
       </c>
-      <c r="M7" s="53" t="n">
+      <c r="M7" s="54" t="n">
         <v>145.7</v>
       </c>
-      <c r="N7" s="53" t="n">
+      <c r="N7" s="54" t="n">
         <v>153.82</v>
       </c>
-      <c r="O7" s="53" t="n">
+      <c r="O7" s="54" t="n">
         <v>132.99</v>
       </c>
-      <c r="P7" s="53" t="n">
+      <c r="P7" s="54" t="n">
         <v>147.32</v>
       </c>
-      <c r="Q7" s="53" t="n">
+      <c r="Q7" s="54" t="n">
         <v>140.16</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="50" t="n">
+      <c r="A8" s="51" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="52" t="inlineStr">
+      <c r="B8" s="53" t="inlineStr">
         <is>
           <t>FR8</t>
         </is>
       </c>
-      <c r="C8" s="53" t="n">
+      <c r="C8" s="54" t="n">
         <v>79.51000000000001</v>
       </c>
-      <c r="D8" s="53" t="n">
+      <c r="D8" s="54" t="n">
         <v>86.45999999999999</v>
       </c>
-      <c r="E8" s="53" t="n">
+      <c r="E8" s="54" t="n">
         <v>93.66</v>
       </c>
-      <c r="F8" s="53" t="n">
+      <c r="F8" s="54" t="n">
         <v>101.12</v>
       </c>
-      <c r="G8" s="53" t="n">
+      <c r="G8" s="54" t="n">
         <v>82.98999999999999</v>
       </c>
-      <c r="H8" s="53" t="n">
+      <c r="H8" s="54" t="n">
         <v>86.45999999999999</v>
       </c>
-      <c r="I8" s="53" t="n">
+      <c r="I8" s="54" t="n">
         <v>93.66</v>
       </c>
-      <c r="J8" s="53" t="n">
+      <c r="J8" s="54" t="n">
         <v>97.39</v>
       </c>
-      <c r="K8" s="53" t="n">
+      <c r="K8" s="54" t="n">
         <v>81.59999999999999</v>
       </c>
-      <c r="L8" s="53" t="n">
+      <c r="L8" s="54" t="n">
         <v>86.45999999999999</v>
       </c>
-      <c r="M8" s="53" t="n">
+      <c r="M8" s="54" t="n">
         <v>93.66</v>
       </c>
-      <c r="N8" s="53" t="n">
+      <c r="N8" s="54" t="n">
         <v>98.88</v>
       </c>
-      <c r="O8" s="53" t="n">
+      <c r="O8" s="54" t="n">
         <v>85.48999999999999</v>
       </c>
-      <c r="P8" s="53" t="n">
+      <c r="P8" s="54" t="n">
         <v>94.7</v>
       </c>
-      <c r="Q8" s="53" t="n">
+      <c r="Q8" s="54" t="n">
         <v>90.09</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="50" t="n">
+      <c r="A9" s="51" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="52" t="inlineStr">
+      <c r="B9" s="53" t="inlineStr">
         <is>
           <t>FR2</t>
         </is>
       </c>
-      <c r="C9" s="53" t="n">
+      <c r="C9" s="54" t="n">
         <v>47.71</v>
       </c>
-      <c r="D9" s="53" t="n">
+      <c r="D9" s="54" t="n">
         <v>51.88</v>
       </c>
-      <c r="E9" s="53" t="n">
+      <c r="E9" s="54" t="n">
         <v>56.2</v>
       </c>
-      <c r="F9" s="53" t="n">
+      <c r="F9" s="54" t="n">
         <v>60.67</v>
       </c>
-      <c r="G9" s="53" t="n">
+      <c r="G9" s="54" t="n">
         <v>49.79</v>
       </c>
-      <c r="H9" s="53" t="n">
+      <c r="H9" s="54" t="n">
         <v>51.88</v>
       </c>
-      <c r="I9" s="53" t="n">
+      <c r="I9" s="54" t="n">
         <v>56.2</v>
       </c>
-      <c r="J9" s="53" t="n">
+      <c r="J9" s="54" t="n">
         <v>58.44</v>
       </c>
-      <c r="K9" s="53" t="n">
+      <c r="K9" s="54" t="n">
         <v>48.96</v>
       </c>
-      <c r="L9" s="53" t="n">
+      <c r="L9" s="54" t="n">
         <v>51.88</v>
       </c>
-      <c r="M9" s="53" t="n">
+      <c r="M9" s="54" t="n">
         <v>56.2</v>
       </c>
-      <c r="N9" s="53" t="n">
+      <c r="N9" s="54" t="n">
         <v>59.33</v>
       </c>
-      <c r="O9" s="53" t="n">
+      <c r="O9" s="54" t="n">
         <v>51.3</v>
       </c>
-      <c r="P9" s="53" t="n">
+      <c r="P9" s="54" t="n">
         <v>56.83</v>
       </c>
-      <c r="Q9" s="53" t="n">
+      <c r="Q9" s="54" t="n">
         <v>54.06</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="50" t="n">
+      <c r="A10" s="51" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="52" t="inlineStr">
+      <c r="B10" s="53" t="inlineStr">
         <is>
           <t>FR5</t>
         </is>
       </c>
-      <c r="C10" s="53" t="n">
+      <c r="C10" s="54" t="n">
         <v>22.09</v>
       </c>
-      <c r="D10" s="53" t="n">
+      <c r="D10" s="54" t="n">
         <v>24.02</v>
       </c>
-      <c r="E10" s="53" t="n">
+      <c r="E10" s="54" t="n">
         <v>26.02</v>
       </c>
-      <c r="F10" s="53" t="n">
+      <c r="F10" s="54" t="n">
         <v>28.09</v>
       </c>
-      <c r="G10" s="53" t="n">
+      <c r="G10" s="54" t="n">
         <v>23.05</v>
       </c>
-      <c r="H10" s="53" t="n">
+      <c r="H10" s="54" t="n">
         <v>24.02</v>
       </c>
-      <c r="I10" s="53" t="n">
+      <c r="I10" s="54" t="n">
         <v>26.02</v>
       </c>
-      <c r="J10" s="53" t="n">
+      <c r="J10" s="54" t="n">
         <v>27.05</v>
       </c>
-      <c r="K10" s="53" t="n">
+      <c r="K10" s="54" t="n">
         <v>22.67</v>
       </c>
-      <c r="L10" s="53" t="n">
+      <c r="L10" s="54" t="n">
         <v>24.02</v>
       </c>
-      <c r="M10" s="53" t="n">
+      <c r="M10" s="54" t="n">
         <v>26.02</v>
       </c>
-      <c r="N10" s="53" t="n">
+      <c r="N10" s="54" t="n">
         <v>27.47</v>
       </c>
-      <c r="O10" s="53" t="n">
+      <c r="O10" s="54" t="n">
         <v>23.75</v>
       </c>
-      <c r="P10" s="53" t="n">
+      <c r="P10" s="54" t="n">
         <v>26.31</v>
       </c>
-      <c r="Q10" s="53" t="n">
+      <c r="Q10" s="54" t="n">
         <v>25.03</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="50" t="n">
+      <c r="A11" s="51" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="52" t="inlineStr">
+      <c r="B11" s="53" t="inlineStr">
         <is>
           <t>FR4</t>
         </is>
       </c>
-      <c r="C11" s="53" t="n">
+      <c r="C11" s="54" t="n">
         <v>15.46</v>
       </c>
-      <c r="D11" s="53" t="n">
+      <c r="D11" s="54" t="n">
         <v>16.81</v>
       </c>
-      <c r="E11" s="53" t="n">
+      <c r="E11" s="54" t="n">
         <v>18.21</v>
       </c>
-      <c r="F11" s="53" t="n">
+      <c r="F11" s="54" t="n">
         <v>19.66</v>
       </c>
-      <c r="G11" s="53" t="n">
+      <c r="G11" s="54" t="n">
         <v>16.14</v>
       </c>
-      <c r="H11" s="53" t="n">
+      <c r="H11" s="54" t="n">
         <v>16.81</v>
       </c>
-      <c r="I11" s="53" t="n">
+      <c r="I11" s="54" t="n">
         <v>18.21</v>
       </c>
-      <c r="J11" s="53" t="n">
+      <c r="J11" s="54" t="n">
         <v>18.94</v>
       </c>
-      <c r="K11" s="53" t="n">
+      <c r="K11" s="54" t="n">
         <v>15.87</v>
       </c>
-      <c r="L11" s="53" t="n">
+      <c r="L11" s="54" t="n">
         <v>16.81</v>
       </c>
-      <c r="M11" s="53" t="n">
+      <c r="M11" s="54" t="n">
         <v>18.21</v>
       </c>
-      <c r="N11" s="53" t="n">
+      <c r="N11" s="54" t="n">
         <v>19.23</v>
       </c>
-      <c r="O11" s="53" t="n">
+      <c r="O11" s="54" t="n">
         <v>16.62</v>
       </c>
-      <c r="P11" s="53" t="n">
+      <c r="P11" s="54" t="n">
         <v>18.41</v>
       </c>
-      <c r="Q11" s="53" t="n">
+      <c r="Q11" s="54" t="n">
         <v>17.52</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="50" t="n">
+      <c r="A12" s="51" t="n">
         <v>9</v>
       </c>
-      <c r="B12" s="52" t="inlineStr">
+      <c r="B12" s="53" t="inlineStr">
         <is>
           <t>FR7</t>
         </is>
       </c>
-      <c r="C12" s="53" t="n">
+      <c r="C12" s="54" t="n">
         <v>3.37</v>
       </c>
-      <c r="D12" s="53" t="n">
+      <c r="D12" s="54" t="n">
         <v>3.66</v>
       </c>
-      <c r="E12" s="53" t="n">
+      <c r="E12" s="54" t="n">
         <v>3.96</v>
       </c>
-      <c r="F12" s="53" t="n">
+      <c r="F12" s="54" t="n">
         <v>4.28</v>
       </c>
-      <c r="G12" s="53" t="n">
+      <c r="G12" s="54" t="n">
         <v>3.51</v>
       </c>
-      <c r="H12" s="53" t="n">
+      <c r="H12" s="54" t="n">
         <v>3.66</v>
       </c>
-      <c r="I12" s="53" t="n">
+      <c r="I12" s="54" t="n">
         <v>3.96</v>
       </c>
-      <c r="J12" s="53" t="n">
+      <c r="J12" s="54" t="n">
         <v>4.12</v>
       </c>
-      <c r="K12" s="53" t="n">
+      <c r="K12" s="54" t="n">
         <v>3.45</v>
       </c>
-      <c r="L12" s="53" t="n">
+      <c r="L12" s="54" t="n">
         <v>3.66</v>
       </c>
-      <c r="M12" s="53" t="n">
+      <c r="M12" s="54" t="n">
         <v>3.96</v>
       </c>
-      <c r="N12" s="53" t="n">
+      <c r="N12" s="54" t="n">
         <v>4.18</v>
       </c>
-      <c r="O12" s="53" t="n">
+      <c r="O12" s="54" t="n">
         <v>3.62</v>
       </c>
-      <c r="P12" s="53" t="n">
+      <c r="P12" s="54" t="n">
         <v>4</v>
       </c>
-      <c r="Q12" s="53" t="n">
+      <c r="Q12" s="54" t="n">
         <v>3.81</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="50" t="n">
+      <c r="A13" s="51" t="n">
         <v>10</v>
       </c>
-      <c r="B13" s="52" t="inlineStr">
+      <c r="B13" s="53" t="inlineStr">
         <is>
           <t>FR6</t>
         </is>
       </c>
-      <c r="C13" s="53" t="n">
+      <c r="C13" s="54" t="n">
         <v>0.68</v>
       </c>
-      <c r="D13" s="53" t="n">
+      <c r="D13" s="54" t="n">
         <v>0.74</v>
       </c>
-      <c r="E13" s="53" t="n">
+      <c r="E13" s="54" t="n">
         <v>0.8</v>
       </c>
-      <c r="F13" s="53" t="n">
+      <c r="F13" s="54" t="n">
         <v>0.86</v>
       </c>
-      <c r="G13" s="53" t="n">
+      <c r="G13" s="54" t="n">
         <v>0.71</v>
       </c>
-      <c r="H13" s="53" t="n">
+      <c r="H13" s="54" t="n">
         <v>0.74</v>
       </c>
-      <c r="I13" s="53" t="n">
+      <c r="I13" s="54" t="n">
         <v>0.8</v>
       </c>
-      <c r="J13" s="53" t="n">
+      <c r="J13" s="54" t="n">
         <v>0.83</v>
       </c>
-      <c r="K13" s="53" t="n">
+      <c r="K13" s="54" t="n">
         <v>0.7</v>
       </c>
-      <c r="L13" s="53" t="n">
+      <c r="L13" s="54" t="n">
         <v>0.74</v>
       </c>
-      <c r="M13" s="53" t="n">
+      <c r="M13" s="54" t="n">
         <v>0.8</v>
       </c>
-      <c r="N13" s="53" t="n">
+      <c r="N13" s="54" t="n">
         <v>0.84</v>
       </c>
-      <c r="O13" s="53" t="n">
+      <c r="O13" s="54" t="n">
         <v>0.73</v>
       </c>
-      <c r="P13" s="53" t="n">
+      <c r="P13" s="54" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="Q13" s="53" t="n">
+      <c r="Q13" s="54" t="n">
         <v>0.77</v>
       </c>
     </row>
     <row r="14"/>
     <row r="15"/>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="51" t="inlineStr">
+      <c r="A16" s="52" t="inlineStr">
         <is>
           <t>2) Итоговая приоритизация после учета взаимосвязанности</t>
         </is>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1">
-      <c r="A17" s="49" t="inlineStr">
+      <c r="A17" s="50" t="inlineStr">
         <is>
           <t>Место</t>
         </is>
       </c>
-      <c r="B17" s="49" t="inlineStr">
+      <c r="B17" s="50" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="C17" s="49" t="inlineStr">
+      <c r="C17" s="50" t="inlineStr">
         <is>
           <t>Исходный центроид</t>
         </is>
       </c>
-      <c r="D17" s="49" t="inlineStr">
+      <c r="D17" s="50" t="inlineStr">
         <is>
           <t>Скорректированный
 центроид</t>
@@ -3204,162 +3207,162 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="50" t="n">
+      <c r="A18" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="B18" s="52" t="inlineStr">
+      <c r="B18" s="53" t="inlineStr">
         <is>
           <t>FR1</t>
         </is>
       </c>
-      <c r="C18" s="53" t="n">
+      <c r="C18" s="54" t="n">
         <v>600.65</v>
       </c>
-      <c r="D18" s="53" t="n">
+      <c r="D18" s="54" t="n">
         <v>600.65</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="50" t="n">
+      <c r="A19" s="51" t="n">
         <v>2</v>
       </c>
-      <c r="B19" s="52" t="inlineStr">
+      <c r="B19" s="53" t="inlineStr">
         <is>
           <t>FR4</t>
         </is>
       </c>
-      <c r="C19" s="53" t="n">
+      <c r="C19" s="54" t="n">
         <v>17.52</v>
       </c>
-      <c r="D19" s="53" t="n">
+      <c r="D19" s="54" t="n">
         <v>600.65</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="50" t="n">
+      <c r="A20" s="51" t="n">
         <v>3</v>
       </c>
-      <c r="B20" s="52" t="inlineStr">
+      <c r="B20" s="53" t="inlineStr">
         <is>
           <t>FR9</t>
         </is>
       </c>
-      <c r="C20" s="53" t="n">
+      <c r="C20" s="54" t="n">
         <v>429.04</v>
       </c>
-      <c r="D20" s="53" t="n">
+      <c r="D20" s="54" t="n">
         <v>429.04</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="50" t="n">
+      <c r="A21" s="51" t="n">
         <v>4</v>
       </c>
-      <c r="B21" s="52" t="inlineStr">
+      <c r="B21" s="53" t="inlineStr">
         <is>
           <t>FR10</t>
         </is>
       </c>
-      <c r="C21" s="53" t="n">
+      <c r="C21" s="54" t="n">
         <v>140.16</v>
       </c>
-      <c r="D21" s="53" t="n">
+      <c r="D21" s="54" t="n">
         <v>429.04</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="50" t="n">
+      <c r="A22" s="51" t="n">
         <v>5</v>
       </c>
-      <c r="B22" s="52" t="inlineStr">
+      <c r="B22" s="53" t="inlineStr">
         <is>
           <t>FR8</t>
         </is>
       </c>
-      <c r="C22" s="53" t="n">
+      <c r="C22" s="54" t="n">
         <v>90.09</v>
       </c>
-      <c r="D22" s="53" t="n">
+      <c r="D22" s="54" t="n">
         <v>429.04</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="50" t="n">
+      <c r="A23" s="51" t="n">
         <v>6</v>
       </c>
-      <c r="B23" s="52" t="inlineStr">
+      <c r="B23" s="53" t="inlineStr">
         <is>
           <t>FR3</t>
         </is>
       </c>
-      <c r="C23" s="53" t="n">
+      <c r="C23" s="54" t="n">
         <v>228.82</v>
       </c>
-      <c r="D23" s="53" t="n">
+      <c r="D23" s="54" t="n">
         <v>228.82</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="50" t="n">
+      <c r="A24" s="51" t="n">
         <v>7</v>
       </c>
-      <c r="B24" s="52" t="inlineStr">
+      <c r="B24" s="53" t="inlineStr">
         <is>
           <t>FR2</t>
         </is>
       </c>
-      <c r="C24" s="53" t="n">
+      <c r="C24" s="54" t="n">
         <v>54.06</v>
       </c>
-      <c r="D24" s="53" t="n">
+      <c r="D24" s="54" t="n">
         <v>54.06</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="50" t="n">
+      <c r="A25" s="51" t="n">
         <v>8</v>
       </c>
-      <c r="B25" s="52" t="inlineStr">
+      <c r="B25" s="53" t="inlineStr">
         <is>
           <t>FR5</t>
         </is>
       </c>
-      <c r="C25" s="53" t="n">
+      <c r="C25" s="54" t="n">
         <v>25.03</v>
       </c>
-      <c r="D25" s="53" t="n">
+      <c r="D25" s="54" t="n">
         <v>25.03</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="50" t="n">
+      <c r="A26" s="51" t="n">
         <v>9</v>
       </c>
-      <c r="B26" s="52" t="inlineStr">
+      <c r="B26" s="53" t="inlineStr">
         <is>
           <t>FR7</t>
         </is>
       </c>
-      <c r="C26" s="53" t="n">
+      <c r="C26" s="54" t="n">
         <v>3.81</v>
       </c>
-      <c r="D26" s="53" t="n">
+      <c r="D26" s="54" t="n">
         <v>3.81</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="50" t="n">
+      <c r="A27" s="51" t="n">
         <v>10</v>
       </c>
-      <c r="B27" s="52" t="inlineStr">
+      <c r="B27" s="53" t="inlineStr">
         <is>
           <t>FR6</t>
         </is>
       </c>
-      <c r="C27" s="53" t="n">
+      <c r="C27" s="54" t="n">
         <v>0.77</v>
       </c>
-      <c r="D27" s="53" t="n">
+      <c r="D27" s="54" t="n">
         <v>3.81</v>
       </c>
     </row>

--- a/2026.02.16_Файлы загрузки и выгрузки данных/Итоги_Fuzzy RICE_один эксперт.xlsx
+++ b/2026.02.16_Файлы загрузки и выгрузки данных/Итоги_Fuzzy RICE_один эксперт.xlsx
@@ -57,7 +57,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="30">
+  <borders count="29">
     <border>
       <left/>
       <right/>
@@ -389,17 +389,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -474,19 +468,22 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2476,10 +2473,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q27"/>
+  <dimension ref="A1:Q34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
@@ -2501,879 +2498,929 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="52" t="inlineStr">
         <is>
-          <t>1) Итоговые нечеткие приоритеты и результаты дефаззификации</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="24" customHeight="1">
-      <c r="A2" s="50" t="inlineStr">
+          <t>Нечеткий RICE - итоговая приоритизация (один эксперт)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="52" t="inlineStr">
+        <is>
+          <t>1) Гиперпараметры модели</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="50" t="inlineStr">
+        <is>
+          <t>Параметр</t>
+        </is>
+      </c>
+      <c r="B4" s="50" t="inlineStr">
+        <is>
+          <t>Значение</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="34" customHeight="1">
+      <c r="A5" s="53" t="inlineStr">
+        <is>
+          <t>a (редукция
+типа CLTR)</t>
+        </is>
+      </c>
+      <c r="B5" s="54" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="6" ht="34" customHeight="1">
+      <c r="A6" s="53" t="inlineStr">
+        <is>
+          <t>alpha (уровень
+альфа-среза)</t>
+        </is>
+      </c>
+      <c r="B6" s="54" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="7"/>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="52" t="inlineStr">
+        <is>
+          <t>2) Итоговые нечеткие приоритеты и результаты дефаззификации</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="50" t="inlineStr">
         <is>
           <t>Приоритизация</t>
         </is>
       </c>
-      <c r="B2" s="50" t="inlineStr">
+      <c r="B9" s="50" t="inlineStr">
         <is>
           <t>Функциональное
 требование</t>
         </is>
       </c>
-      <c r="C2" s="50" t="inlineStr">
+      <c r="C9" s="50" t="inlineStr">
         <is>
           <t>RICE в формате ИНМТ2</t>
         </is>
       </c>
-      <c r="D2" s="50" t="n"/>
-      <c r="E2" s="50" t="n"/>
-      <c r="F2" s="50" t="n"/>
-      <c r="G2" s="50" t="n"/>
-      <c r="H2" s="50" t="n"/>
-      <c r="I2" s="50" t="n"/>
-      <c r="J2" s="50" t="n"/>
-      <c r="K2" s="50" t="inlineStr">
+      <c r="D9" s="50" t="n"/>
+      <c r="E9" s="50" t="n"/>
+      <c r="F9" s="50" t="n"/>
+      <c r="G9" s="50" t="n"/>
+      <c r="H9" s="50" t="n"/>
+      <c r="I9" s="50" t="n"/>
+      <c r="J9" s="50" t="n"/>
+      <c r="K9" s="50" t="inlineStr">
         <is>
           <t>RICE после редукции в ИНМТ1</t>
         </is>
       </c>
-      <c r="L2" s="50" t="n"/>
-      <c r="M2" s="50" t="n"/>
-      <c r="N2" s="50" t="n"/>
-      <c r="O2" s="50" t="inlineStr">
+      <c r="L9" s="50" t="n"/>
+      <c r="M9" s="50" t="n"/>
+      <c r="N9" s="50" t="n"/>
+      <c r="O9" s="50" t="inlineStr">
         <is>
           <t>Альфа-срез</t>
         </is>
       </c>
-      <c r="P2" s="50" t="n"/>
-      <c r="Q2" s="50" t="inlineStr">
+      <c r="P9" s="50" t="n"/>
+      <c r="Q9" s="50" t="inlineStr">
         <is>
           <t>Итог</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="50" t="n"/>
-      <c r="B3" s="50" t="n"/>
-      <c r="C3" s="50" t="inlineStr">
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="50" t="n"/>
+      <c r="B10" s="50" t="n"/>
+      <c r="C10" s="50" t="inlineStr">
         <is>
           <t>x1</t>
         </is>
       </c>
-      <c r="D3" s="50" t="inlineStr">
+      <c r="D10" s="50" t="inlineStr">
         <is>
           <t>x2</t>
         </is>
       </c>
-      <c r="E3" s="50" t="inlineStr">
+      <c r="E10" s="50" t="inlineStr">
         <is>
           <t>x3</t>
         </is>
       </c>
-      <c r="F3" s="50" t="inlineStr">
+      <c r="F10" s="50" t="inlineStr">
         <is>
           <t>x4</t>
         </is>
       </c>
-      <c r="G3" s="50" t="inlineStr">
+      <c r="G10" s="50" t="inlineStr">
         <is>
           <t>x5</t>
         </is>
       </c>
-      <c r="H3" s="50" t="inlineStr">
+      <c r="H10" s="50" t="inlineStr">
         <is>
           <t>x6</t>
         </is>
       </c>
-      <c r="I3" s="50" t="inlineStr">
+      <c r="I10" s="50" t="inlineStr">
         <is>
           <t>x7</t>
         </is>
       </c>
-      <c r="J3" s="50" t="inlineStr">
+      <c r="J10" s="50" t="inlineStr">
         <is>
           <t>x8</t>
         </is>
       </c>
-      <c r="K3" s="50" t="inlineStr">
+      <c r="K10" s="50" t="inlineStr">
         <is>
           <t>x1</t>
         </is>
       </c>
-      <c r="L3" s="50" t="inlineStr">
+      <c r="L10" s="50" t="inlineStr">
         <is>
           <t>x2</t>
         </is>
       </c>
-      <c r="M3" s="50" t="inlineStr">
+      <c r="M10" s="50" t="inlineStr">
         <is>
           <t>x3</t>
         </is>
       </c>
-      <c r="N3" s="50" t="inlineStr">
+      <c r="N10" s="50" t="inlineStr">
         <is>
           <t>x4</t>
         </is>
       </c>
-      <c r="O3" s="50" t="inlineStr">
+      <c r="O10" s="50" t="inlineStr">
         <is>
           <t>Левый</t>
         </is>
       </c>
-      <c r="P3" s="50" t="inlineStr">
+      <c r="P10" s="50" t="inlineStr">
         <is>
           <t>Правый</t>
         </is>
       </c>
-      <c r="Q3" s="50" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="51" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" s="53" t="inlineStr">
-        <is>
-          <t>FR1</t>
-        </is>
-      </c>
-      <c r="C4" s="54" t="n">
-        <v>530.0700000000001</v>
-      </c>
-      <c r="D4" s="54" t="n">
-        <v>576.42</v>
-      </c>
-      <c r="E4" s="54" t="n">
-        <v>624.42</v>
-      </c>
-      <c r="F4" s="54" t="n">
-        <v>674.13</v>
-      </c>
-      <c r="G4" s="54" t="n">
-        <v>553.24</v>
-      </c>
-      <c r="H4" s="54" t="n">
-        <v>576.42</v>
-      </c>
-      <c r="I4" s="54" t="n">
-        <v>624.42</v>
-      </c>
-      <c r="J4" s="54" t="n">
-        <v>649.28</v>
-      </c>
-      <c r="K4" s="54" t="n">
-        <v>543.97</v>
-      </c>
-      <c r="L4" s="54" t="n">
-        <v>576.42</v>
-      </c>
-      <c r="M4" s="54" t="n">
-        <v>624.42</v>
-      </c>
-      <c r="N4" s="54" t="n">
-        <v>659.22</v>
-      </c>
-      <c r="O4" s="54" t="n">
-        <v>569.9299999999999</v>
-      </c>
-      <c r="P4" s="54" t="n">
-        <v>631.38</v>
-      </c>
-      <c r="Q4" s="54" t="n">
-        <v>600.65</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="51" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="53" t="inlineStr">
-        <is>
-          <t>FR9</t>
-        </is>
-      </c>
-      <c r="C5" s="54" t="n">
-        <v>378.62</v>
-      </c>
-      <c r="D5" s="54" t="n">
-        <v>411.73</v>
-      </c>
-      <c r="E5" s="54" t="n">
-        <v>446.02</v>
-      </c>
-      <c r="F5" s="54" t="n">
-        <v>481.52</v>
-      </c>
-      <c r="G5" s="54" t="n">
-        <v>395.17</v>
-      </c>
-      <c r="H5" s="54" t="n">
-        <v>411.73</v>
-      </c>
-      <c r="I5" s="54" t="n">
-        <v>446.02</v>
-      </c>
-      <c r="J5" s="54" t="n">
-        <v>463.77</v>
-      </c>
-      <c r="K5" s="54" t="n">
-        <v>388.55</v>
-      </c>
-      <c r="L5" s="54" t="n">
-        <v>411.73</v>
-      </c>
-      <c r="M5" s="54" t="n">
-        <v>446.02</v>
-      </c>
-      <c r="N5" s="54" t="n">
-        <v>470.87</v>
-      </c>
-      <c r="O5" s="54" t="n">
-        <v>407.09</v>
-      </c>
-      <c r="P5" s="54" t="n">
-        <v>450.99</v>
-      </c>
-      <c r="Q5" s="54" t="n">
-        <v>429.04</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="51" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="53" t="inlineStr">
-        <is>
-          <t>FR3</t>
-        </is>
-      </c>
-      <c r="C6" s="54" t="n">
-        <v>201.93</v>
-      </c>
-      <c r="D6" s="54" t="n">
-        <v>219.59</v>
-      </c>
-      <c r="E6" s="54" t="n">
-        <v>237.88</v>
-      </c>
-      <c r="F6" s="54" t="n">
-        <v>256.81</v>
-      </c>
-      <c r="G6" s="54" t="n">
-        <v>210.76</v>
-      </c>
-      <c r="H6" s="54" t="n">
-        <v>219.59</v>
-      </c>
-      <c r="I6" s="54" t="n">
-        <v>237.88</v>
-      </c>
-      <c r="J6" s="54" t="n">
-        <v>247.34</v>
-      </c>
-      <c r="K6" s="54" t="n">
-        <v>207.23</v>
-      </c>
-      <c r="L6" s="54" t="n">
-        <v>219.59</v>
-      </c>
-      <c r="M6" s="54" t="n">
-        <v>237.88</v>
-      </c>
-      <c r="N6" s="54" t="n">
-        <v>251.13</v>
-      </c>
-      <c r="O6" s="54" t="n">
-        <v>217.12</v>
-      </c>
-      <c r="P6" s="54" t="n">
-        <v>240.53</v>
-      </c>
-      <c r="Q6" s="54" t="n">
-        <v>228.82</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="51" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" s="53" t="inlineStr">
-        <is>
-          <t>FR10</t>
-        </is>
-      </c>
-      <c r="C7" s="54" t="n">
-        <v>123.68</v>
-      </c>
-      <c r="D7" s="54" t="n">
-        <v>134.5</v>
-      </c>
-      <c r="E7" s="54" t="n">
-        <v>145.7</v>
-      </c>
-      <c r="F7" s="54" t="n">
-        <v>157.3</v>
-      </c>
-      <c r="G7" s="54" t="n">
-        <v>129.09</v>
-      </c>
-      <c r="H7" s="54" t="n">
-        <v>134.5</v>
-      </c>
-      <c r="I7" s="54" t="n">
-        <v>145.7</v>
-      </c>
-      <c r="J7" s="54" t="n">
-        <v>151.5</v>
-      </c>
-      <c r="K7" s="54" t="n">
-        <v>126.93</v>
-      </c>
-      <c r="L7" s="54" t="n">
-        <v>134.5</v>
-      </c>
-      <c r="M7" s="54" t="n">
-        <v>145.7</v>
-      </c>
-      <c r="N7" s="54" t="n">
-        <v>153.82</v>
-      </c>
-      <c r="O7" s="54" t="n">
-        <v>132.99</v>
-      </c>
-      <c r="P7" s="54" t="n">
-        <v>147.32</v>
-      </c>
-      <c r="Q7" s="54" t="n">
-        <v>140.16</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="51" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="53" t="inlineStr">
-        <is>
-          <t>FR8</t>
-        </is>
-      </c>
-      <c r="C8" s="54" t="n">
-        <v>79.51000000000001</v>
-      </c>
-      <c r="D8" s="54" t="n">
-        <v>86.45999999999999</v>
-      </c>
-      <c r="E8" s="54" t="n">
-        <v>93.66</v>
-      </c>
-      <c r="F8" s="54" t="n">
-        <v>101.12</v>
-      </c>
-      <c r="G8" s="54" t="n">
-        <v>82.98999999999999</v>
-      </c>
-      <c r="H8" s="54" t="n">
-        <v>86.45999999999999</v>
-      </c>
-      <c r="I8" s="54" t="n">
-        <v>93.66</v>
-      </c>
-      <c r="J8" s="54" t="n">
-        <v>97.39</v>
-      </c>
-      <c r="K8" s="54" t="n">
-        <v>81.59999999999999</v>
-      </c>
-      <c r="L8" s="54" t="n">
-        <v>86.45999999999999</v>
-      </c>
-      <c r="M8" s="54" t="n">
-        <v>93.66</v>
-      </c>
-      <c r="N8" s="54" t="n">
-        <v>98.88</v>
-      </c>
-      <c r="O8" s="54" t="n">
-        <v>85.48999999999999</v>
-      </c>
-      <c r="P8" s="54" t="n">
-        <v>94.7</v>
-      </c>
-      <c r="Q8" s="54" t="n">
-        <v>90.09</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="51" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" s="53" t="inlineStr">
-        <is>
-          <t>FR2</t>
-        </is>
-      </c>
-      <c r="C9" s="54" t="n">
-        <v>47.71</v>
-      </c>
-      <c r="D9" s="54" t="n">
-        <v>51.88</v>
-      </c>
-      <c r="E9" s="54" t="n">
-        <v>56.2</v>
-      </c>
-      <c r="F9" s="54" t="n">
-        <v>60.67</v>
-      </c>
-      <c r="G9" s="54" t="n">
-        <v>49.79</v>
-      </c>
-      <c r="H9" s="54" t="n">
-        <v>51.88</v>
-      </c>
-      <c r="I9" s="54" t="n">
-        <v>56.2</v>
-      </c>
-      <c r="J9" s="54" t="n">
-        <v>58.44</v>
-      </c>
-      <c r="K9" s="54" t="n">
-        <v>48.96</v>
-      </c>
-      <c r="L9" s="54" t="n">
-        <v>51.88</v>
-      </c>
-      <c r="M9" s="54" t="n">
-        <v>56.2</v>
-      </c>
-      <c r="N9" s="54" t="n">
-        <v>59.33</v>
-      </c>
-      <c r="O9" s="54" t="n">
-        <v>51.3</v>
-      </c>
-      <c r="P9" s="54" t="n">
-        <v>56.83</v>
-      </c>
-      <c r="Q9" s="54" t="n">
-        <v>54.06</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="51" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" s="53" t="inlineStr">
-        <is>
-          <t>FR5</t>
-        </is>
-      </c>
-      <c r="C10" s="54" t="n">
-        <v>22.09</v>
-      </c>
-      <c r="D10" s="54" t="n">
-        <v>24.02</v>
-      </c>
-      <c r="E10" s="54" t="n">
-        <v>26.02</v>
-      </c>
-      <c r="F10" s="54" t="n">
-        <v>28.09</v>
-      </c>
-      <c r="G10" s="54" t="n">
-        <v>23.05</v>
-      </c>
-      <c r="H10" s="54" t="n">
-        <v>24.02</v>
-      </c>
-      <c r="I10" s="54" t="n">
-        <v>26.02</v>
-      </c>
-      <c r="J10" s="54" t="n">
-        <v>27.05</v>
-      </c>
-      <c r="K10" s="54" t="n">
-        <v>22.67</v>
-      </c>
-      <c r="L10" s="54" t="n">
-        <v>24.02</v>
-      </c>
-      <c r="M10" s="54" t="n">
-        <v>26.02</v>
-      </c>
-      <c r="N10" s="54" t="n">
-        <v>27.47</v>
-      </c>
-      <c r="O10" s="54" t="n">
-        <v>23.75</v>
-      </c>
-      <c r="P10" s="54" t="n">
-        <v>26.31</v>
-      </c>
-      <c r="Q10" s="54" t="n">
-        <v>25.03</v>
-      </c>
+      <c r="Q10" s="50" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="51" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" s="53" t="inlineStr">
-        <is>
-          <t>FR4</t>
+        <v>1</v>
+      </c>
+      <c r="B11" s="55" t="inlineStr">
+        <is>
+          <t>FR1</t>
         </is>
       </c>
       <c r="C11" s="54" t="n">
-        <v>15.46</v>
+        <v>530.0700000000001</v>
       </c>
       <c r="D11" s="54" t="n">
-        <v>16.81</v>
+        <v>576.42</v>
       </c>
       <c r="E11" s="54" t="n">
-        <v>18.21</v>
+        <v>624.42</v>
       </c>
       <c r="F11" s="54" t="n">
-        <v>19.66</v>
+        <v>674.13</v>
       </c>
       <c r="G11" s="54" t="n">
-        <v>16.14</v>
+        <v>553.24</v>
       </c>
       <c r="H11" s="54" t="n">
-        <v>16.81</v>
+        <v>576.42</v>
       </c>
       <c r="I11" s="54" t="n">
-        <v>18.21</v>
+        <v>624.42</v>
       </c>
       <c r="J11" s="54" t="n">
-        <v>18.94</v>
+        <v>649.28</v>
       </c>
       <c r="K11" s="54" t="n">
-        <v>15.87</v>
+        <v>543.97</v>
       </c>
       <c r="L11" s="54" t="n">
-        <v>16.81</v>
+        <v>576.42</v>
       </c>
       <c r="M11" s="54" t="n">
-        <v>18.21</v>
+        <v>624.42</v>
       </c>
       <c r="N11" s="54" t="n">
-        <v>19.23</v>
+        <v>659.22</v>
       </c>
       <c r="O11" s="54" t="n">
-        <v>16.62</v>
+        <v>569.9299999999999</v>
       </c>
       <c r="P11" s="54" t="n">
-        <v>18.41</v>
+        <v>631.38</v>
       </c>
       <c r="Q11" s="54" t="n">
-        <v>17.52</v>
+        <v>600.65</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="51" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" s="53" t="inlineStr">
-        <is>
-          <t>FR7</t>
+        <v>2</v>
+      </c>
+      <c r="B12" s="55" t="inlineStr">
+        <is>
+          <t>FR9</t>
         </is>
       </c>
       <c r="C12" s="54" t="n">
-        <v>3.37</v>
+        <v>378.62</v>
       </c>
       <c r="D12" s="54" t="n">
-        <v>3.66</v>
+        <v>411.73</v>
       </c>
       <c r="E12" s="54" t="n">
-        <v>3.96</v>
+        <v>446.02</v>
       </c>
       <c r="F12" s="54" t="n">
-        <v>4.28</v>
+        <v>481.52</v>
       </c>
       <c r="G12" s="54" t="n">
-        <v>3.51</v>
+        <v>395.17</v>
       </c>
       <c r="H12" s="54" t="n">
-        <v>3.66</v>
+        <v>411.73</v>
       </c>
       <c r="I12" s="54" t="n">
-        <v>3.96</v>
+        <v>446.02</v>
       </c>
       <c r="J12" s="54" t="n">
-        <v>4.12</v>
+        <v>463.77</v>
       </c>
       <c r="K12" s="54" t="n">
-        <v>3.45</v>
+        <v>388.55</v>
       </c>
       <c r="L12" s="54" t="n">
-        <v>3.66</v>
+        <v>411.73</v>
       </c>
       <c r="M12" s="54" t="n">
-        <v>3.96</v>
+        <v>446.02</v>
       </c>
       <c r="N12" s="54" t="n">
-        <v>4.18</v>
+        <v>470.87</v>
       </c>
       <c r="O12" s="54" t="n">
-        <v>3.62</v>
+        <v>407.09</v>
       </c>
       <c r="P12" s="54" t="n">
-        <v>4</v>
+        <v>450.99</v>
       </c>
       <c r="Q12" s="54" t="n">
-        <v>3.81</v>
+        <v>429.04</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="51" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" s="55" t="inlineStr">
+        <is>
+          <t>FR3</t>
+        </is>
+      </c>
+      <c r="C13" s="54" t="n">
+        <v>201.93</v>
+      </c>
+      <c r="D13" s="54" t="n">
+        <v>219.59</v>
+      </c>
+      <c r="E13" s="54" t="n">
+        <v>237.88</v>
+      </c>
+      <c r="F13" s="54" t="n">
+        <v>256.81</v>
+      </c>
+      <c r="G13" s="54" t="n">
+        <v>210.76</v>
+      </c>
+      <c r="H13" s="54" t="n">
+        <v>219.59</v>
+      </c>
+      <c r="I13" s="54" t="n">
+        <v>237.88</v>
+      </c>
+      <c r="J13" s="54" t="n">
+        <v>247.34</v>
+      </c>
+      <c r="K13" s="54" t="n">
+        <v>207.23</v>
+      </c>
+      <c r="L13" s="54" t="n">
+        <v>219.59</v>
+      </c>
+      <c r="M13" s="54" t="n">
+        <v>237.88</v>
+      </c>
+      <c r="N13" s="54" t="n">
+        <v>251.13</v>
+      </c>
+      <c r="O13" s="54" t="n">
+        <v>217.12</v>
+      </c>
+      <c r="P13" s="54" t="n">
+        <v>240.53</v>
+      </c>
+      <c r="Q13" s="54" t="n">
+        <v>228.82</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="51" t="n">
+        <v>4</v>
+      </c>
+      <c r="B14" s="55" t="inlineStr">
+        <is>
+          <t>FR10</t>
+        </is>
+      </c>
+      <c r="C14" s="54" t="n">
+        <v>123.68</v>
+      </c>
+      <c r="D14" s="54" t="n">
+        <v>134.5</v>
+      </c>
+      <c r="E14" s="54" t="n">
+        <v>145.7</v>
+      </c>
+      <c r="F14" s="54" t="n">
+        <v>157.3</v>
+      </c>
+      <c r="G14" s="54" t="n">
+        <v>129.09</v>
+      </c>
+      <c r="H14" s="54" t="n">
+        <v>134.5</v>
+      </c>
+      <c r="I14" s="54" t="n">
+        <v>145.7</v>
+      </c>
+      <c r="J14" s="54" t="n">
+        <v>151.5</v>
+      </c>
+      <c r="K14" s="54" t="n">
+        <v>126.93</v>
+      </c>
+      <c r="L14" s="54" t="n">
+        <v>134.5</v>
+      </c>
+      <c r="M14" s="54" t="n">
+        <v>145.7</v>
+      </c>
+      <c r="N14" s="54" t="n">
+        <v>153.82</v>
+      </c>
+      <c r="O14" s="54" t="n">
+        <v>132.99</v>
+      </c>
+      <c r="P14" s="54" t="n">
+        <v>147.32</v>
+      </c>
+      <c r="Q14" s="54" t="n">
+        <v>140.16</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="51" t="n">
+        <v>5</v>
+      </c>
+      <c r="B15" s="55" t="inlineStr">
+        <is>
+          <t>FR8</t>
+        </is>
+      </c>
+      <c r="C15" s="54" t="n">
+        <v>79.51000000000001</v>
+      </c>
+      <c r="D15" s="54" t="n">
+        <v>86.45999999999999</v>
+      </c>
+      <c r="E15" s="54" t="n">
+        <v>93.66</v>
+      </c>
+      <c r="F15" s="54" t="n">
+        <v>101.12</v>
+      </c>
+      <c r="G15" s="54" t="n">
+        <v>82.98999999999999</v>
+      </c>
+      <c r="H15" s="54" t="n">
+        <v>86.45999999999999</v>
+      </c>
+      <c r="I15" s="54" t="n">
+        <v>93.66</v>
+      </c>
+      <c r="J15" s="54" t="n">
+        <v>97.39</v>
+      </c>
+      <c r="K15" s="54" t="n">
+        <v>81.59999999999999</v>
+      </c>
+      <c r="L15" s="54" t="n">
+        <v>86.45999999999999</v>
+      </c>
+      <c r="M15" s="54" t="n">
+        <v>93.66</v>
+      </c>
+      <c r="N15" s="54" t="n">
+        <v>98.88</v>
+      </c>
+      <c r="O15" s="54" t="n">
+        <v>85.48999999999999</v>
+      </c>
+      <c r="P15" s="54" t="n">
+        <v>94.7</v>
+      </c>
+      <c r="Q15" s="54" t="n">
+        <v>90.09</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="51" t="n">
+        <v>6</v>
+      </c>
+      <c r="B16" s="55" t="inlineStr">
+        <is>
+          <t>FR2</t>
+        </is>
+      </c>
+      <c r="C16" s="54" t="n">
+        <v>47.71</v>
+      </c>
+      <c r="D16" s="54" t="n">
+        <v>51.88</v>
+      </c>
+      <c r="E16" s="54" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="F16" s="54" t="n">
+        <v>60.67</v>
+      </c>
+      <c r="G16" s="54" t="n">
+        <v>49.79</v>
+      </c>
+      <c r="H16" s="54" t="n">
+        <v>51.88</v>
+      </c>
+      <c r="I16" s="54" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="J16" s="54" t="n">
+        <v>58.44</v>
+      </c>
+      <c r="K16" s="54" t="n">
+        <v>48.96</v>
+      </c>
+      <c r="L16" s="54" t="n">
+        <v>51.88</v>
+      </c>
+      <c r="M16" s="54" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="N16" s="54" t="n">
+        <v>59.33</v>
+      </c>
+      <c r="O16" s="54" t="n">
+        <v>51.3</v>
+      </c>
+      <c r="P16" s="54" t="n">
+        <v>56.83</v>
+      </c>
+      <c r="Q16" s="54" t="n">
+        <v>54.06</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="51" t="n">
+        <v>7</v>
+      </c>
+      <c r="B17" s="55" t="inlineStr">
+        <is>
+          <t>FR5</t>
+        </is>
+      </c>
+      <c r="C17" s="54" t="n">
+        <v>22.09</v>
+      </c>
+      <c r="D17" s="54" t="n">
+        <v>24.02</v>
+      </c>
+      <c r="E17" s="54" t="n">
+        <v>26.02</v>
+      </c>
+      <c r="F17" s="54" t="n">
+        <v>28.09</v>
+      </c>
+      <c r="G17" s="54" t="n">
+        <v>23.05</v>
+      </c>
+      <c r="H17" s="54" t="n">
+        <v>24.02</v>
+      </c>
+      <c r="I17" s="54" t="n">
+        <v>26.02</v>
+      </c>
+      <c r="J17" s="54" t="n">
+        <v>27.05</v>
+      </c>
+      <c r="K17" s="54" t="n">
+        <v>22.67</v>
+      </c>
+      <c r="L17" s="54" t="n">
+        <v>24.02</v>
+      </c>
+      <c r="M17" s="54" t="n">
+        <v>26.02</v>
+      </c>
+      <c r="N17" s="54" t="n">
+        <v>27.47</v>
+      </c>
+      <c r="O17" s="54" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="P17" s="54" t="n">
+        <v>26.31</v>
+      </c>
+      <c r="Q17" s="54" t="n">
+        <v>25.03</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="51" t="n">
+        <v>8</v>
+      </c>
+      <c r="B18" s="55" t="inlineStr">
+        <is>
+          <t>FR4</t>
+        </is>
+      </c>
+      <c r="C18" s="54" t="n">
+        <v>15.46</v>
+      </c>
+      <c r="D18" s="54" t="n">
+        <v>16.81</v>
+      </c>
+      <c r="E18" s="54" t="n">
+        <v>18.21</v>
+      </c>
+      <c r="F18" s="54" t="n">
+        <v>19.66</v>
+      </c>
+      <c r="G18" s="54" t="n">
+        <v>16.14</v>
+      </c>
+      <c r="H18" s="54" t="n">
+        <v>16.81</v>
+      </c>
+      <c r="I18" s="54" t="n">
+        <v>18.21</v>
+      </c>
+      <c r="J18" s="54" t="n">
+        <v>18.94</v>
+      </c>
+      <c r="K18" s="54" t="n">
+        <v>15.87</v>
+      </c>
+      <c r="L18" s="54" t="n">
+        <v>16.81</v>
+      </c>
+      <c r="M18" s="54" t="n">
+        <v>18.21</v>
+      </c>
+      <c r="N18" s="54" t="n">
+        <v>19.23</v>
+      </c>
+      <c r="O18" s="54" t="n">
+        <v>16.62</v>
+      </c>
+      <c r="P18" s="54" t="n">
+        <v>18.41</v>
+      </c>
+      <c r="Q18" s="54" t="n">
+        <v>17.52</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="51" t="n">
+        <v>9</v>
+      </c>
+      <c r="B19" s="55" t="inlineStr">
+        <is>
+          <t>FR7</t>
+        </is>
+      </c>
+      <c r="C19" s="54" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="D19" s="54" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="E19" s="54" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="F19" s="54" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="G19" s="54" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="H19" s="54" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="I19" s="54" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="J19" s="54" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="K19" s="54" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L19" s="54" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="M19" s="54" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="N19" s="54" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="O19" s="54" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="P19" s="54" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q19" s="54" t="n">
+        <v>3.81</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="51" t="n">
         <v>10</v>
       </c>
-      <c r="B13" s="53" t="inlineStr">
+      <c r="B20" s="55" t="inlineStr">
         <is>
           <t>FR6</t>
         </is>
       </c>
-      <c r="C13" s="54" t="n">
+      <c r="C20" s="54" t="n">
         <v>0.68</v>
       </c>
-      <c r="D13" s="54" t="n">
+      <c r="D20" s="54" t="n">
         <v>0.74</v>
       </c>
-      <c r="E13" s="54" t="n">
+      <c r="E20" s="54" t="n">
         <v>0.8</v>
       </c>
-      <c r="F13" s="54" t="n">
+      <c r="F20" s="54" t="n">
         <v>0.86</v>
       </c>
-      <c r="G13" s="54" t="n">
+      <c r="G20" s="54" t="n">
         <v>0.71</v>
       </c>
-      <c r="H13" s="54" t="n">
+      <c r="H20" s="54" t="n">
         <v>0.74</v>
       </c>
-      <c r="I13" s="54" t="n">
+      <c r="I20" s="54" t="n">
         <v>0.8</v>
       </c>
-      <c r="J13" s="54" t="n">
+      <c r="J20" s="54" t="n">
         <v>0.83</v>
       </c>
-      <c r="K13" s="54" t="n">
+      <c r="K20" s="54" t="n">
         <v>0.7</v>
       </c>
-      <c r="L13" s="54" t="n">
+      <c r="L20" s="54" t="n">
         <v>0.74</v>
       </c>
-      <c r="M13" s="54" t="n">
+      <c r="M20" s="54" t="n">
         <v>0.8</v>
       </c>
-      <c r="N13" s="54" t="n">
+      <c r="N20" s="54" t="n">
         <v>0.84</v>
       </c>
-      <c r="O13" s="54" t="n">
+      <c r="O20" s="54" t="n">
         <v>0.73</v>
       </c>
-      <c r="P13" s="54" t="n">
+      <c r="P20" s="54" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="Q13" s="54" t="n">
+      <c r="Q20" s="54" t="n">
         <v>0.77</v>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="52" t="inlineStr">
-        <is>
-          <t>2) Итоговая приоритизация после учета взаимосвязанности</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="36" customHeight="1">
-      <c r="A17" s="50" t="inlineStr">
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="52" t="inlineStr">
+        <is>
+          <t>3) Итоговая приоритизация после учета взаимосвязанности</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="50" t="inlineStr">
         <is>
           <t>Место</t>
         </is>
       </c>
-      <c r="B17" s="50" t="inlineStr">
+      <c r="B24" s="50" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="C17" s="50" t="inlineStr">
+      <c r="C24" s="50" t="inlineStr">
         <is>
           <t>Исходный центроид</t>
         </is>
       </c>
-      <c r="D17" s="50" t="inlineStr">
+      <c r="D24" s="50" t="inlineStr">
         <is>
           <t>Скорректированный
 центроид</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="51" t="n">
-        <v>1</v>
-      </c>
-      <c r="B18" s="53" t="inlineStr">
-        <is>
-          <t>FR1</t>
-        </is>
-      </c>
-      <c r="C18" s="54" t="n">
-        <v>600.65</v>
-      </c>
-      <c r="D18" s="54" t="n">
-        <v>600.65</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="51" t="n">
-        <v>2</v>
-      </c>
-      <c r="B19" s="53" t="inlineStr">
-        <is>
-          <t>FR4</t>
-        </is>
-      </c>
-      <c r="C19" s="54" t="n">
-        <v>17.52</v>
-      </c>
-      <c r="D19" s="54" t="n">
-        <v>600.65</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="51" t="n">
-        <v>3</v>
-      </c>
-      <c r="B20" s="53" t="inlineStr">
-        <is>
-          <t>FR9</t>
-        </is>
-      </c>
-      <c r="C20" s="54" t="n">
-        <v>429.04</v>
-      </c>
-      <c r="D20" s="54" t="n">
-        <v>429.04</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="51" t="n">
-        <v>4</v>
-      </c>
-      <c r="B21" s="53" t="inlineStr">
-        <is>
-          <t>FR10</t>
-        </is>
-      </c>
-      <c r="C21" s="54" t="n">
-        <v>140.16</v>
-      </c>
-      <c r="D21" s="54" t="n">
-        <v>429.04</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="51" t="n">
-        <v>5</v>
-      </c>
-      <c r="B22" s="53" t="inlineStr">
-        <is>
-          <t>FR8</t>
-        </is>
-      </c>
-      <c r="C22" s="54" t="n">
-        <v>90.09</v>
-      </c>
-      <c r="D22" s="54" t="n">
-        <v>429.04</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="51" t="n">
-        <v>6</v>
-      </c>
-      <c r="B23" s="53" t="inlineStr">
-        <is>
-          <t>FR3</t>
-        </is>
-      </c>
-      <c r="C23" s="54" t="n">
-        <v>228.82</v>
-      </c>
-      <c r="D23" s="54" t="n">
-        <v>228.82</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="51" t="n">
-        <v>7</v>
-      </c>
-      <c r="B24" s="53" t="inlineStr">
-        <is>
-          <t>FR2</t>
-        </is>
-      </c>
-      <c r="C24" s="54" t="n">
-        <v>54.06</v>
-      </c>
-      <c r="D24" s="54" t="n">
-        <v>54.06</v>
-      </c>
-    </row>
     <row r="25">
       <c r="A25" s="51" t="n">
-        <v>8</v>
-      </c>
-      <c r="B25" s="53" t="inlineStr">
-        <is>
-          <t>FR5</t>
+        <v>1</v>
+      </c>
+      <c r="B25" s="55" t="inlineStr">
+        <is>
+          <t>FR1</t>
         </is>
       </c>
       <c r="C25" s="54" t="n">
-        <v>25.03</v>
+        <v>600.65</v>
       </c>
       <c r="D25" s="54" t="n">
-        <v>25.03</v>
+        <v>600.65</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="51" t="n">
-        <v>9</v>
-      </c>
-      <c r="B26" s="53" t="inlineStr">
-        <is>
-          <t>FR7</t>
+        <v>2</v>
+      </c>
+      <c r="B26" s="55" t="inlineStr">
+        <is>
+          <t>FR4</t>
         </is>
       </c>
       <c r="C26" s="54" t="n">
-        <v>3.81</v>
+        <v>17.52</v>
       </c>
       <c r="D26" s="54" t="n">
-        <v>3.81</v>
+        <v>600.65</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="51" t="n">
+        <v>3</v>
+      </c>
+      <c r="B27" s="55" t="inlineStr">
+        <is>
+          <t>FR9</t>
+        </is>
+      </c>
+      <c r="C27" s="54" t="n">
+        <v>429.04</v>
+      </c>
+      <c r="D27" s="54" t="n">
+        <v>429.04</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="51" t="n">
+        <v>4</v>
+      </c>
+      <c r="B28" s="55" t="inlineStr">
+        <is>
+          <t>FR10</t>
+        </is>
+      </c>
+      <c r="C28" s="54" t="n">
+        <v>140.16</v>
+      </c>
+      <c r="D28" s="54" t="n">
+        <v>429.04</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="51" t="n">
+        <v>5</v>
+      </c>
+      <c r="B29" s="55" t="inlineStr">
+        <is>
+          <t>FR8</t>
+        </is>
+      </c>
+      <c r="C29" s="54" t="n">
+        <v>90.09</v>
+      </c>
+      <c r="D29" s="54" t="n">
+        <v>429.04</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="51" t="n">
+        <v>6</v>
+      </c>
+      <c r="B30" s="55" t="inlineStr">
+        <is>
+          <t>FR3</t>
+        </is>
+      </c>
+      <c r="C30" s="54" t="n">
+        <v>228.82</v>
+      </c>
+      <c r="D30" s="54" t="n">
+        <v>228.82</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="51" t="n">
+        <v>7</v>
+      </c>
+      <c r="B31" s="55" t="inlineStr">
+        <is>
+          <t>FR2</t>
+        </is>
+      </c>
+      <c r="C31" s="54" t="n">
+        <v>54.06</v>
+      </c>
+      <c r="D31" s="54" t="n">
+        <v>54.06</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="51" t="n">
+        <v>8</v>
+      </c>
+      <c r="B32" s="55" t="inlineStr">
+        <is>
+          <t>FR5</t>
+        </is>
+      </c>
+      <c r="C32" s="54" t="n">
+        <v>25.03</v>
+      </c>
+      <c r="D32" s="54" t="n">
+        <v>25.03</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="51" t="n">
+        <v>9</v>
+      </c>
+      <c r="B33" s="55" t="inlineStr">
+        <is>
+          <t>FR7</t>
+        </is>
+      </c>
+      <c r="C33" s="54" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="D33" s="54" t="n">
+        <v>3.81</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="51" t="n">
         <v>10</v>
       </c>
-      <c r="B27" s="53" t="inlineStr">
+      <c r="B34" s="55" t="inlineStr">
         <is>
           <t>FR6</t>
         </is>
       </c>
-      <c r="C27" s="54" t="n">
+      <c r="C34" s="54" t="n">
         <v>0.77</v>
       </c>
-      <c r="D27" s="54" t="n">
+      <c r="D34" s="54" t="n">
         <v>3.81</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="O2:P2"/>
-    <mergeCell ref="C2:J2"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="K2:N2"/>
-    <mergeCell ref="Q2:Q3"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="Q9:Q10"/>
+    <mergeCell ref="O9:P9"/>
+    <mergeCell ref="K9:N9"/>
+    <mergeCell ref="C9:J9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/2026.02.16_Файлы загрузки и выгрузки данных/Итоги_Fuzzy RICE_один эксперт.xlsx
+++ b/2026.02.16_Файлы загрузки и выгрузки данных/Итоги_Fuzzy RICE_один эксперт.xlsx
@@ -2506,7 +2506,7 @@
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="52" t="inlineStr">
         <is>
-          <t>1) Гиперпараметры модели</t>
+          <t>1) Параметры модели</t>
         </is>
       </c>
     </row>

--- a/2026.02.16_Файлы загрузки и выгрузки данных/Итоги_Fuzzy RICE_один эксперт.xlsx
+++ b/2026.02.16_Файлы загрузки и выгрузки данных/Итоги_Fuzzy RICE_один эксперт.xlsx
@@ -316,36 +316,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="medium">
@@ -382,6 +352,36 @@
         <color indexed="64"/>
       </right>
       <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
         <color indexed="64"/>
       </top>
       <bottom style="thin">
@@ -425,15 +425,10 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -449,19 +444,24 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -834,12 +834,12 @@
   <sheetData>
     <row r="1" ht="15.75" customHeight="1" thickBot="1"/>
     <row r="2">
-      <c r="A2" s="39" t="inlineStr">
+      <c r="A2" s="32" t="inlineStr">
         <is>
           <t>Feature</t>
         </is>
       </c>
-      <c r="B2" s="31" t="inlineStr">
+      <c r="B2" s="38" t="inlineStr">
         <is>
           <t>R, Reach (Охват), количество человек</t>
         </is>
@@ -851,7 +851,7 @@
       <c r="G2" s="41" t="n"/>
       <c r="H2" s="41" t="n"/>
       <c r="I2" s="42" t="n"/>
-      <c r="J2" s="31" t="inlineStr">
+      <c r="J2" s="38" t="inlineStr">
         <is>
           <t>I, Impact (Влияние), оценка в баллах</t>
         </is>
@@ -863,7 +863,7 @@
       <c r="O2" s="41" t="n"/>
       <c r="P2" s="41" t="n"/>
       <c r="Q2" s="42" t="n"/>
-      <c r="R2" s="31" t="inlineStr">
+      <c r="R2" s="38" t="inlineStr">
         <is>
           <t>С, Confidence (Уверенность), коэффициент от 0,5 до 1</t>
         </is>
@@ -875,7 +875,7 @@
       <c r="W2" s="41" t="n"/>
       <c r="X2" s="41" t="n"/>
       <c r="Y2" s="42" t="n"/>
-      <c r="Z2" s="31" t="inlineStr">
+      <c r="Z2" s="38" t="inlineStr">
         <is>
           <t>E, Effort (Трудозатраты), количество недель</t>
         </is>
@@ -956,7 +956,7 @@
       <c r="AG3" s="48" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="40" t="inlineStr">
+      <c r="A4" s="31" t="inlineStr">
         <is>
           <t>FR1</t>
         </is>
@@ -1059,7 +1059,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="40" t="inlineStr">
+      <c r="A5" s="31" t="inlineStr">
         <is>
           <t>FR2</t>
         </is>
@@ -1095,10 +1095,10 @@
         <v>2.97</v>
       </c>
       <c r="L5" s="22" t="n">
-        <v>3.03</v>
+        <v>3</v>
       </c>
       <c r="M5" s="23" t="n">
-        <v>3.09</v>
+        <v>3</v>
       </c>
       <c r="N5" s="24" t="n">
         <v>2.94</v>
@@ -1107,10 +1107,10 @@
         <v>2.97</v>
       </c>
       <c r="P5" s="22" t="n">
-        <v>3.03</v>
+        <v>3</v>
       </c>
       <c r="Q5" s="25" t="n">
-        <v>3.06</v>
+        <v>3</v>
       </c>
       <c r="R5" s="21" t="n">
         <v>0.873</v>
@@ -1162,7 +1162,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="40" t="inlineStr">
+      <c r="A6" s="31" t="inlineStr">
         <is>
           <t>FR3</t>
         </is>
@@ -1265,7 +1265,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="40" t="inlineStr">
+      <c r="A7" s="31" t="inlineStr">
         <is>
           <t>FR4</t>
         </is>
@@ -1368,7 +1368,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="40" t="inlineStr">
+      <c r="A8" s="31" t="inlineStr">
         <is>
           <t>FR5</t>
         </is>
@@ -1404,10 +1404,10 @@
         <v>2.97</v>
       </c>
       <c r="L8" s="22" t="n">
-        <v>3.03</v>
+        <v>3</v>
       </c>
       <c r="M8" s="23" t="n">
-        <v>3.09</v>
+        <v>3</v>
       </c>
       <c r="N8" s="24" t="n">
         <v>2.94</v>
@@ -1416,10 +1416,10 @@
         <v>2.97</v>
       </c>
       <c r="P8" s="22" t="n">
-        <v>3.03</v>
+        <v>3</v>
       </c>
       <c r="Q8" s="25" t="n">
-        <v>3.06</v>
+        <v>3</v>
       </c>
       <c r="R8" s="21" t="n">
         <v>0.485</v>
@@ -1471,7 +1471,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="40" t="inlineStr">
+      <c r="A9" s="31" t="inlineStr">
         <is>
           <t>FR6</t>
         </is>
@@ -1531,10 +1531,10 @@
         <v>0.99</v>
       </c>
       <c r="T9" s="22" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="U9" s="23" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="V9" s="24" t="n">
         <v>0.98</v>
@@ -1543,10 +1543,10 @@
         <v>0.99</v>
       </c>
       <c r="X9" s="22" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y9" s="25" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Z9" s="21" t="n">
         <v>12.61</v>
@@ -1574,7 +1574,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="40" t="inlineStr">
+      <c r="A10" s="31" t="inlineStr">
         <is>
           <t>FR7</t>
         </is>
@@ -1677,7 +1677,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="40" t="inlineStr">
+      <c r="A11" s="31" t="inlineStr">
         <is>
           <t>FR8</t>
         </is>
@@ -1780,7 +1780,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="40" t="inlineStr">
+      <c r="A12" s="31" t="inlineStr">
         <is>
           <t>FR9</t>
         </is>
@@ -1883,7 +1883,7 @@
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A13" s="40" t="inlineStr">
+      <c r="A13" s="31" t="inlineStr">
         <is>
           <t>FR10</t>
         </is>
@@ -1992,14 +1992,14 @@
     <mergeCell ref="Z2:AG2"/>
     <mergeCell ref="Z3:AC3"/>
     <mergeCell ref="F3:I3"/>
+    <mergeCell ref="AD3:AG3"/>
+    <mergeCell ref="J3:M3"/>
     <mergeCell ref="B2:I2"/>
-    <mergeCell ref="J3:M3"/>
-    <mergeCell ref="AD3:AG3"/>
     <mergeCell ref="N3:Q3"/>
     <mergeCell ref="R2:Y2"/>
     <mergeCell ref="J2:Q2"/>
+    <mergeCell ref="B3:E3"/>
     <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B3:E3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2962,10 +2962,10 @@
         <v>51.88</v>
       </c>
       <c r="E16" s="54" t="n">
-        <v>56.2</v>
+        <v>55.64</v>
       </c>
       <c r="F16" s="54" t="n">
-        <v>60.67</v>
+        <v>58.97</v>
       </c>
       <c r="G16" s="54" t="n">
         <v>49.79</v>
@@ -2974,10 +2974,10 @@
         <v>51.88</v>
       </c>
       <c r="I16" s="54" t="n">
-        <v>56.2</v>
+        <v>55.64</v>
       </c>
       <c r="J16" s="54" t="n">
-        <v>58.44</v>
+        <v>57.31</v>
       </c>
       <c r="K16" s="54" t="n">
         <v>48.96</v>
@@ -2986,19 +2986,19 @@
         <v>51.88</v>
       </c>
       <c r="M16" s="54" t="n">
-        <v>56.2</v>
+        <v>55.64</v>
       </c>
       <c r="N16" s="54" t="n">
-        <v>59.33</v>
+        <v>57.97</v>
       </c>
       <c r="O16" s="54" t="n">
         <v>51.3</v>
       </c>
       <c r="P16" s="54" t="n">
-        <v>56.83</v>
+        <v>56.11</v>
       </c>
       <c r="Q16" s="54" t="n">
-        <v>54.06</v>
+        <v>53.7</v>
       </c>
     </row>
     <row r="17">
@@ -3017,10 +3017,10 @@
         <v>24.02</v>
       </c>
       <c r="E17" s="54" t="n">
-        <v>26.02</v>
+        <v>25.76</v>
       </c>
       <c r="F17" s="54" t="n">
-        <v>28.09</v>
+        <v>27.3</v>
       </c>
       <c r="G17" s="54" t="n">
         <v>23.05</v>
@@ -3029,10 +3029,10 @@
         <v>24.02</v>
       </c>
       <c r="I17" s="54" t="n">
-        <v>26.02</v>
+        <v>25.76</v>
       </c>
       <c r="J17" s="54" t="n">
-        <v>27.05</v>
+        <v>26.53</v>
       </c>
       <c r="K17" s="54" t="n">
         <v>22.67</v>
@@ -3041,19 +3041,19 @@
         <v>24.02</v>
       </c>
       <c r="M17" s="54" t="n">
-        <v>26.02</v>
+        <v>25.76</v>
       </c>
       <c r="N17" s="54" t="n">
-        <v>27.47</v>
+        <v>26.84</v>
       </c>
       <c r="O17" s="54" t="n">
         <v>23.75</v>
       </c>
       <c r="P17" s="54" t="n">
-        <v>26.31</v>
+        <v>25.98</v>
       </c>
       <c r="Q17" s="54" t="n">
-        <v>25.03</v>
+        <v>24.87</v>
       </c>
     </row>
     <row r="18">
@@ -3182,10 +3182,10 @@
         <v>0.74</v>
       </c>
       <c r="E20" s="54" t="n">
-        <v>0.8</v>
+        <v>0.79</v>
       </c>
       <c r="F20" s="54" t="n">
-        <v>0.86</v>
+        <v>0.84</v>
       </c>
       <c r="G20" s="54" t="n">
         <v>0.71</v>
@@ -3194,10 +3194,10 @@
         <v>0.74</v>
       </c>
       <c r="I20" s="54" t="n">
-        <v>0.8</v>
+        <v>0.79</v>
       </c>
       <c r="J20" s="54" t="n">
-        <v>0.83</v>
+        <v>0.82</v>
       </c>
       <c r="K20" s="54" t="n">
         <v>0.7</v>
@@ -3206,16 +3206,16 @@
         <v>0.74</v>
       </c>
       <c r="M20" s="54" t="n">
-        <v>0.8</v>
+        <v>0.79</v>
       </c>
       <c r="N20" s="54" t="n">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="O20" s="54" t="n">
         <v>0.73</v>
       </c>
       <c r="P20" s="54" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="Q20" s="54" t="n">
         <v>0.77</v>
@@ -3359,10 +3359,10 @@
         </is>
       </c>
       <c r="C31" s="54" t="n">
-        <v>54.06</v>
+        <v>53.7</v>
       </c>
       <c r="D31" s="54" t="n">
-        <v>54.06</v>
+        <v>53.7</v>
       </c>
     </row>
     <row r="32">
@@ -3375,10 +3375,10 @@
         </is>
       </c>
       <c r="C32" s="54" t="n">
-        <v>25.03</v>
+        <v>24.87</v>
       </c>
       <c r="D32" s="54" t="n">
-        <v>25.03</v>
+        <v>24.87</v>
       </c>
     </row>
     <row r="33">
